--- a/excel/Investavimas Rima.xlsx
+++ b/excel/Investavimas Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC9D250-2D90-40AE-9A2D-BEC606679E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81414D25-56C4-4E11-BE5D-E27F1E97A215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="20">
   <si>
     <t>Data</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Loanch</t>
+  </si>
+  <si>
+    <t>Income</t>
   </si>
 </sst>
 </file>
@@ -353,6 +356,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -372,9 +378,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -691,105 +694,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BL20"/>
+  <dimension ref="A1:BO21"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="7" width="10.7109375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26" t="s">
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26" t="s">
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26" t="s">
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26" t="s">
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26" t="s">
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26" t="s">
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
       <c r="AC1" s="3"/>
-      <c r="AD1" s="27" t="s">
+      <c r="AD1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
-      <c r="AJ1" s="27"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
       <c r="AK1" s="3"/>
-      <c r="AL1" s="27" t="s">
+      <c r="AL1" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="AM1" s="27"/>
-      <c r="AN1" s="27"/>
-      <c r="AO1" s="27"/>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="27"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
       <c r="AS1" s="17"/>
-      <c r="AT1" s="27" t="s">
+      <c r="AT1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="AU1" s="27"/>
-      <c r="AV1" s="27"/>
-      <c r="AW1" s="27"/>
-      <c r="AX1" s="27"/>
-      <c r="AY1" s="27"/>
-      <c r="AZ1" s="27"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
+      <c r="AW1" s="28"/>
+      <c r="AX1" s="28"/>
+      <c r="AY1" s="28"/>
+      <c r="AZ1" s="28"/>
       <c r="BA1" s="18"/>
-      <c r="BB1" s="21"/>
-      <c r="BC1" s="22"/>
-      <c r="BD1" s="22"/>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="22"/>
-      <c r="BG1" s="22"/>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
-      <c r="BJ1" s="22"/>
-      <c r="BK1" s="23"/>
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="23"/>
+      <c r="BD1" s="23"/>
+      <c r="BE1" s="23"/>
+      <c r="BF1" s="23"/>
+      <c r="BG1" s="23"/>
+      <c r="BH1" s="23"/>
+      <c r="BI1" s="23"/>
+      <c r="BJ1" s="23"/>
+      <c r="BK1" s="24"/>
     </row>
     <row r="2" spans="1:64" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
@@ -2086,7 +2089,7 @@
         <f t="shared" si="10"/>
         <v>1.835</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="21">
         <v>400</v>
       </c>
       <c r="L8" s="4">
@@ -2303,7 +2306,7 @@
         <f t="shared" si="10"/>
         <v>1.835</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="21">
         <v>400</v>
       </c>
       <c r="L9" s="4">
@@ -2521,7 +2524,7 @@
         <f t="shared" si="10"/>
         <v>1.835</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="21">
         <v>400</v>
       </c>
       <c r="L10" s="4">
@@ -2739,7 +2742,7 @@
         <f t="shared" si="10"/>
         <v>1.835</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="21">
         <v>500</v>
       </c>
       <c r="L11" s="4">
@@ -2957,7 +2960,7 @@
         <f t="shared" ref="J12" si="38">(I12-H12)/H12</f>
         <v>1.8366666666666664</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="21">
         <v>500</v>
       </c>
       <c r="L12" s="4">
@@ -3176,7 +3179,7 @@
         <f t="shared" ref="J13" si="43">(I13-H13)/H13</f>
         <v>1.8366666666666664</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="21">
         <v>500</v>
       </c>
       <c r="L13" s="4">
@@ -3394,7 +3397,7 @@
         <f t="shared" ref="J14" si="49">(I14-H14)/H14</f>
         <v>1.8366666666666664</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="21">
         <v>500</v>
       </c>
       <c r="L14" s="4">
@@ -3612,7 +3615,7 @@
         <f t="shared" ref="J15" si="55">(I15-H15)/H15</f>
         <v>1.8366666666666664</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="21">
         <v>500</v>
       </c>
       <c r="L15" s="4">
@@ -3830,7 +3833,7 @@
         <f t="shared" ref="J16" si="72">(I16-H16)/H16</f>
         <v>1.8366666666666664</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="21">
         <v>500</v>
       </c>
       <c r="L16" s="4">
@@ -3867,7 +3870,7 @@
         <v>50.1</v>
       </c>
       <c r="V16" s="12">
-        <f>(U16-T16)/T16</f>
+        <f t="shared" ref="V16:V21" si="76">(U16-T16)/T16</f>
         <v>0.25250000000000006</v>
       </c>
       <c r="W16" s="5">
@@ -3889,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" ref="AD16" si="76">A16</f>
+        <f t="shared" ref="AD16" si="77">A16</f>
         <v>46142</v>
       </c>
       <c r="AE16" s="4">
@@ -3905,15 +3908,15 @@
         <v>894.61999999999989</v>
       </c>
       <c r="AH16" s="4">
-        <f t="shared" ref="AH16" si="77">AG16-AE16</f>
+        <f t="shared" ref="AH16" si="78">AG16-AE16</f>
         <v>44.619999999999891</v>
       </c>
       <c r="AI16" s="13">
-        <f t="shared" ref="AI16" si="78">AH16/AE16</f>
+        <f t="shared" ref="AI16" si="79">AH16/AE16</f>
         <v>5.2494117647058698E-2</v>
       </c>
       <c r="AJ16" s="4">
-        <f t="shared" ref="AJ16" si="79">AH16-AH15</f>
+        <f t="shared" ref="AJ16" si="80">AH16-AH15</f>
         <v>53.709999999999809</v>
       </c>
       <c r="AK16" s="10"/>
@@ -3975,31 +3978,31 @@
         <v>70.899999999999636</v>
       </c>
       <c r="BB16" s="8">
-        <f t="shared" ref="BB16" si="80">A16</f>
+        <f t="shared" ref="BB16" si="81">A16</f>
         <v>46142</v>
       </c>
       <c r="BC16" s="4">
-        <f t="shared" ref="BC16" si="81">(C16-B16)-(C15-B15)</f>
+        <f t="shared" ref="BC16" si="82">(C16-B16)-(C15-B15)</f>
         <v>27.909999999999968</v>
       </c>
       <c r="BD16" s="4">
-        <f t="shared" ref="BD16" si="82">(F16-E16)-(F15-E15)</f>
+        <f t="shared" ref="BD16" si="83">(F16-E16)-(F15-E15)</f>
         <v>25.799999999999955</v>
       </c>
       <c r="BE16" s="4">
-        <f t="shared" ref="BE16" si="83">(I16-H16)-(I15-H15)</f>
+        <f t="shared" ref="BE16" si="84">(I16-H16)-(I15-H15)</f>
         <v>0</v>
       </c>
       <c r="BF16" s="4">
-        <f t="shared" ref="BF16" si="84">(L16-K16)-(L15-K15)</f>
+        <f t="shared" ref="BF16" si="85">(L16-K16)-(L15-K15)</f>
         <v>4.6800000000000637</v>
       </c>
       <c r="BG16" s="4">
-        <f t="shared" ref="BG16" si="85">(O16-N16)-(O15-N15)</f>
+        <f t="shared" ref="BG16" si="86">(O16-N16)-(O15-N15)</f>
         <v>2.32000000000005</v>
       </c>
       <c r="BH16" s="4">
-        <f t="shared" ref="BH16" si="86">(R16-Q16)-(R15-Q15)</f>
+        <f t="shared" ref="BH16" si="87">(R16-Q16)-(R15-Q15)</f>
         <v>10.089999999999918</v>
       </c>
       <c r="BI16" s="4">
@@ -4011,11 +4014,11 @@
         <v>0</v>
       </c>
       <c r="BK16" s="4">
-        <f t="shared" ref="BK16" si="87">(AA16-Z16)-(AA15-Z15)</f>
+        <f t="shared" ref="BK16" si="88">(AA16-Z16)-(AA15-Z15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>46173</v>
       </c>
@@ -4026,7 +4029,7 @@
         <v>527.07000000000005</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17" si="88">(C17-B17)/B17</f>
+        <f t="shared" ref="D17" si="89">(C17-B17)/B17</f>
         <v>9.8062500000000108E-2</v>
       </c>
       <c r="E17" s="5">
@@ -4036,7 +4039,7 @@
         <v>544.42999999999995</v>
       </c>
       <c r="G17" s="11">
-        <f t="shared" ref="G17" si="89">(F17-E17)/E17</f>
+        <f t="shared" ref="G17" si="90">(F17-E17)/E17</f>
         <v>8.8859999999999897E-2</v>
       </c>
       <c r="H17" s="5">
@@ -4046,17 +4049,17 @@
         <v>85.35</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" ref="J17" si="90">(I17-H17)/H17</f>
+        <f t="shared" ref="J17" si="91">(I17-H17)/H17</f>
         <v>1.8449999999999998</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="21">
         <v>515.39</v>
       </c>
       <c r="L17" s="4">
         <v>551.17999999999995</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" ref="M17" si="91">(L17-K17)/K17</f>
+        <f t="shared" ref="M17" si="92">(L17-K17)/K17</f>
         <v>6.9442558062826135E-2</v>
       </c>
       <c r="N17" s="5">
@@ -4066,7 +4069,7 @@
         <v>684.13</v>
       </c>
       <c r="P17" s="12">
-        <f t="shared" ref="P17" si="92">(O17-N17)/N17</f>
+        <f t="shared" ref="P17" si="93">(O17-N17)/N17</f>
         <v>0.10343548387096774</v>
       </c>
       <c r="Q17" s="5">
@@ -4076,7 +4079,7 @@
         <v>666.19</v>
       </c>
       <c r="S17" s="12">
-        <f t="shared" ref="S17" si="93">(R17-Q17)/Q17</f>
+        <f t="shared" ref="S17" si="94">(R17-Q17)/Q17</f>
         <v>9.2114754098360743E-2</v>
       </c>
       <c r="T17" s="5">
@@ -4086,7 +4089,7 @@
         <v>80.5</v>
       </c>
       <c r="V17" s="12">
-        <f>(U17-T17)/T17</f>
+        <f t="shared" si="76"/>
         <v>0.15</v>
       </c>
       <c r="W17" s="5">
@@ -4108,36 +4111,36 @@
         <v>0</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" ref="AD17" si="94">A17</f>
+        <f t="shared" ref="AD17" si="95">A17</f>
         <v>46173</v>
       </c>
       <c r="AE17" s="4">
-        <f t="shared" ref="AE17" si="95">B17+E17</f>
+        <f t="shared" ref="AE17" si="96">B17+E17</f>
         <v>980</v>
       </c>
       <c r="AF17" s="4">
-        <f t="shared" ref="AF17" si="96">AE17-AE16</f>
+        <f t="shared" ref="AF17" si="97">AE17-AE16</f>
         <v>130</v>
       </c>
       <c r="AG17" s="4">
-        <f t="shared" ref="AG17" si="97">C17+F17</f>
+        <f t="shared" ref="AG17" si="98">C17+F17</f>
         <v>1071.5</v>
       </c>
       <c r="AH17" s="4">
-        <f t="shared" ref="AH17" si="98">AG17-AE17</f>
+        <f t="shared" ref="AH17" si="99">AG17-AE17</f>
         <v>91.5</v>
       </c>
       <c r="AI17" s="13">
-        <f t="shared" ref="AI17" si="99">AH17/AE17</f>
+        <f t="shared" ref="AI17" si="100">AH17/AE17</f>
         <v>9.3367346938775506E-2</v>
       </c>
       <c r="AJ17" s="4">
-        <f t="shared" ref="AJ17" si="100">AH17-AH16</f>
+        <f t="shared" ref="AJ17" si="101">AH17-AH16</f>
         <v>46.880000000000109</v>
       </c>
       <c r="AK17" s="10"/>
       <c r="AL17" s="8">
-        <f t="shared" ref="AL17" si="101">A17</f>
+        <f t="shared" ref="AL17" si="102">A17</f>
         <v>46173</v>
       </c>
       <c r="AM17" s="4">
@@ -4145,7 +4148,7 @@
         <v>1845.3899999999999</v>
       </c>
       <c r="AN17" s="4">
-        <f t="shared" ref="AN17" si="102">AM17-AM16</f>
+        <f t="shared" ref="AN17" si="103">AM17-AM16</f>
         <v>45.389999999999873</v>
       </c>
       <c r="AO17" s="4">
@@ -4153,72 +4156,72 @@
         <v>2067.35</v>
       </c>
       <c r="AP17" s="4">
-        <f t="shared" ref="AP17" si="103">AO17-AM17</f>
+        <f t="shared" ref="AP17" si="104">AO17-AM17</f>
         <v>221.96000000000004</v>
       </c>
       <c r="AQ17" s="13">
-        <f t="shared" ref="AQ17" si="104">AP17/AM17</f>
+        <f t="shared" ref="AQ17" si="105">AP17/AM17</f>
         <v>0.12027809839654494</v>
       </c>
       <c r="AR17" s="4">
-        <f t="shared" ref="AR17" si="105">AP17-AP16</f>
+        <f t="shared" ref="AR17" si="106">AP17-AP16</f>
         <v>-6.7799999999999727</v>
       </c>
       <c r="AS17" s="10"/>
       <c r="AT17" s="8">
-        <f t="shared" ref="AT17" si="106">A17</f>
+        <f t="shared" ref="AT17" si="107">A17</f>
         <v>46173</v>
       </c>
       <c r="AU17" s="4">
-        <f t="shared" ref="AU17" si="107">AE17+AM17</f>
+        <f t="shared" ref="AU17" si="108">AE17+AM17</f>
         <v>2825.39</v>
       </c>
       <c r="AV17" s="4">
-        <f t="shared" ref="AV17" si="108">AU17-AU16</f>
+        <f t="shared" ref="AV17" si="109">AU17-AU16</f>
         <v>175.38999999999987</v>
       </c>
       <c r="AW17" s="4">
-        <f t="shared" ref="AW17" si="109">AG17+AO17</f>
+        <f t="shared" ref="AW17" si="110">AG17+AO17</f>
         <v>3138.85</v>
       </c>
       <c r="AX17" s="4">
-        <f t="shared" ref="AX17" si="110">AW17-AU17</f>
+        <f t="shared" ref="AX17" si="111">AW17-AU17</f>
         <v>313.46000000000004</v>
       </c>
       <c r="AY17" s="13">
-        <f t="shared" ref="AY17" si="111">AX17/AU17</f>
+        <f t="shared" ref="AY17" si="112">AX17/AU17</f>
         <v>0.1109439758758968</v>
       </c>
       <c r="AZ17" s="4">
-        <f t="shared" ref="AZ17" si="112">AX17-AX16</f>
+        <f t="shared" ref="AZ17" si="113">AX17-AX16</f>
         <v>40.100000000000364</v>
       </c>
       <c r="BB17" s="8">
-        <f t="shared" ref="BB17" si="113">A17</f>
+        <f t="shared" ref="BB17" si="114">A17</f>
         <v>46173</v>
       </c>
       <c r="BC17" s="4">
-        <f t="shared" ref="BC17" si="114">(C17-B17)-(C16-B16)</f>
+        <f t="shared" ref="BC17" si="115">(C17-B17)-(C16-B16)</f>
         <v>20.480000000000075</v>
       </c>
       <c r="BD17" s="4">
-        <f t="shared" ref="BD17" si="115">(F17-E17)-(F16-E16)</f>
+        <f t="shared" ref="BD17" si="116">(F17-E17)-(F16-E16)</f>
         <v>26.399999999999977</v>
       </c>
       <c r="BE17" s="4">
-        <f t="shared" ref="BE17" si="116">(I17-H17)-(I16-H16)</f>
+        <f t="shared" ref="BE17" si="117">(I17-H17)-(I16-H16)</f>
         <v>0.25</v>
       </c>
       <c r="BF17" s="4">
-        <f t="shared" ref="BF17" si="117">(L17-K17)-(L16-K16)</f>
+        <f t="shared" ref="BF17" si="118">(L17-K17)-(L16-K16)</f>
         <v>-13.450000000000045</v>
       </c>
       <c r="BG17" s="4">
-        <f t="shared" ref="BG17" si="118">(O17-N17)-(O16-N16)</f>
+        <f t="shared" ref="BG17" si="119">(O17-N17)-(O16-N16)</f>
         <v>4.3799999999999955</v>
       </c>
       <c r="BH17" s="4">
-        <f t="shared" ref="BH17" si="119">(R17-Q17)-(R16-Q16)</f>
+        <f t="shared" ref="BH17" si="120">(R17-Q17)-(R16-Q16)</f>
         <v>1.6400000000001</v>
       </c>
       <c r="BI17" s="4">
@@ -4230,11 +4233,11 @@
         <v>0</v>
       </c>
       <c r="BK17" s="4">
-        <f t="shared" ref="BK17" si="120">(AA17-Z17)-(AA16-Z16)</f>
+        <f t="shared" ref="BK17" si="121">(AA17-Z17)-(AA16-Z16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>46203</v>
       </c>
@@ -4245,7 +4248,7 @@
         <v>560.79999999999995</v>
       </c>
       <c r="D18" s="11">
-        <f t="shared" ref="D18" si="121">(C18-B18)/B18</f>
+        <f t="shared" ref="D18" si="122">(C18-B18)/B18</f>
         <v>9.9607843137254806E-2</v>
       </c>
       <c r="E18" s="5">
@@ -4255,7 +4258,7 @@
         <v>655.75</v>
       </c>
       <c r="G18" s="11">
-        <f t="shared" ref="G18" si="122">(F18-E18)/E18</f>
+        <f t="shared" ref="G18" si="123">(F18-E18)/E18</f>
         <v>9.2916666666666661E-2</v>
       </c>
       <c r="H18" s="5">
@@ -4265,17 +4268,17 @@
         <v>85.35</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" ref="J18" si="123">(I18-H18)/H18</f>
+        <f t="shared" ref="J18" si="124">(I18-H18)/H18</f>
         <v>1.8449999999999998</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="21">
         <v>624.35</v>
       </c>
       <c r="L18" s="4">
         <v>663.89</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" ref="M18" si="124">(L18-K18)/K18</f>
+        <f t="shared" ref="M18" si="125">(L18-K18)/K18</f>
         <v>6.3329863057579816E-2</v>
       </c>
       <c r="N18" s="5">
@@ -4285,7 +4288,7 @@
         <v>693.4</v>
       </c>
       <c r="P18" s="12">
-        <f t="shared" ref="P18" si="125">(O18-N18)/N18</f>
+        <f t="shared" ref="P18" si="126">(O18-N18)/N18</f>
         <v>0.11838709677419351</v>
       </c>
       <c r="Q18" s="5">
@@ -4295,7 +4298,7 @@
         <v>667.84</v>
       </c>
       <c r="S18" s="12">
-        <f t="shared" ref="S18" si="126">(R18-Q18)/Q18</f>
+        <f t="shared" ref="S18" si="127">(R18-Q18)/Q18</f>
         <v>9.4819672131147587E-2</v>
       </c>
       <c r="T18" s="5">
@@ -4305,7 +4308,7 @@
         <v>81.400000000000006</v>
       </c>
       <c r="V18" s="12">
-        <f>(U18-T18)/T18</f>
+        <f t="shared" si="76"/>
         <v>0.16285714285714295</v>
       </c>
       <c r="W18" s="5">
@@ -4327,36 +4330,36 @@
         <v>0</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="127">A18</f>
+        <f t="shared" ref="AD18" si="128">A18</f>
         <v>46203</v>
       </c>
       <c r="AE18" s="4">
-        <f t="shared" ref="AE18" si="128">B18+E18</f>
+        <f t="shared" ref="AE18" si="129">B18+E18</f>
         <v>1110</v>
       </c>
       <c r="AF18" s="4">
-        <f t="shared" ref="AF18" si="129">AE18-AE17</f>
+        <f t="shared" ref="AF18" si="130">AE18-AE17</f>
         <v>130</v>
       </c>
       <c r="AG18" s="4">
-        <f t="shared" ref="AG18" si="130">C18+F18</f>
+        <f t="shared" ref="AG18" si="131">C18+F18</f>
         <v>1216.55</v>
       </c>
       <c r="AH18" s="4">
-        <f t="shared" ref="AH18" si="131">AG18-AE18</f>
+        <f t="shared" ref="AH18" si="132">AG18-AE18</f>
         <v>106.54999999999995</v>
       </c>
       <c r="AI18" s="13">
-        <f t="shared" ref="AI18" si="132">AH18/AE18</f>
+        <f t="shared" ref="AI18" si="133">AH18/AE18</f>
         <v>9.5990990990990954E-2</v>
       </c>
       <c r="AJ18" s="4">
-        <f t="shared" ref="AJ18" si="133">AH18-AH17</f>
+        <f t="shared" ref="AJ18" si="134">AH18-AH17</f>
         <v>15.049999999999955</v>
       </c>
       <c r="AK18" s="10"/>
       <c r="AL18" s="8">
-        <f t="shared" ref="AL18" si="134">A18</f>
+        <f t="shared" ref="AL18" si="135">A18</f>
         <v>46203</v>
       </c>
       <c r="AM18" s="4">
@@ -4364,7 +4367,7 @@
         <v>1954.35</v>
       </c>
       <c r="AN18" s="4">
-        <f t="shared" ref="AN18" si="135">AM18-AM17</f>
+        <f t="shared" ref="AN18" si="136">AM18-AM17</f>
         <v>108.96000000000004</v>
       </c>
       <c r="AO18" s="4">
@@ -4372,72 +4375,72 @@
         <v>2191.88</v>
       </c>
       <c r="AP18" s="4">
-        <f t="shared" ref="AP18" si="136">AO18-AM18</f>
+        <f t="shared" ref="AP18" si="137">AO18-AM18</f>
         <v>237.5300000000002</v>
       </c>
       <c r="AQ18" s="13">
-        <f t="shared" ref="AQ18" si="137">AP18/AM18</f>
+        <f t="shared" ref="AQ18" si="138">AP18/AM18</f>
         <v>0.12153913065725187</v>
       </c>
       <c r="AR18" s="4">
-        <f t="shared" ref="AR18" si="138">AP18-AP17</f>
+        <f t="shared" ref="AR18" si="139">AP18-AP17</f>
         <v>15.570000000000164</v>
       </c>
       <c r="AS18" s="10"/>
       <c r="AT18" s="8">
-        <f t="shared" ref="AT18" si="139">A18</f>
+        <f t="shared" ref="AT18" si="140">A18</f>
         <v>46203</v>
       </c>
       <c r="AU18" s="4">
-        <f t="shared" ref="AU18" si="140">AE18+AM18</f>
+        <f t="shared" ref="AU18" si="141">AE18+AM18</f>
         <v>3064.35</v>
       </c>
       <c r="AV18" s="4">
-        <f t="shared" ref="AV18" si="141">AU18-AU17</f>
+        <f t="shared" ref="AV18" si="142">AU18-AU17</f>
         <v>238.96000000000004</v>
       </c>
       <c r="AW18" s="4">
-        <f t="shared" ref="AW18" si="142">AG18+AO18</f>
+        <f t="shared" ref="AW18" si="143">AG18+AO18</f>
         <v>3408.4300000000003</v>
       </c>
       <c r="AX18" s="4">
-        <f t="shared" ref="AX18" si="143">AW18-AU18</f>
+        <f t="shared" ref="AX18" si="144">AW18-AU18</f>
         <v>344.08000000000038</v>
       </c>
       <c r="AY18" s="13">
-        <f t="shared" ref="AY18" si="144">AX18/AU18</f>
+        <f t="shared" ref="AY18" si="145">AX18/AU18</f>
         <v>0.11228482386150419</v>
       </c>
       <c r="AZ18" s="4">
-        <f t="shared" ref="AZ18" si="145">AX18-AX17</f>
+        <f t="shared" ref="AZ18" si="146">AX18-AX17</f>
         <v>30.620000000000346</v>
       </c>
       <c r="BB18" s="8">
-        <f t="shared" ref="BB18" si="146">A18</f>
+        <f t="shared" ref="BB18" si="147">A18</f>
         <v>46203</v>
       </c>
       <c r="BC18" s="4">
-        <f t="shared" ref="BC18" si="147">(C18-B18)-(C17-B17)</f>
+        <f t="shared" ref="BC18" si="148">(C18-B18)-(C17-B17)</f>
         <v>3.7299999999999045</v>
       </c>
       <c r="BD18" s="4">
-        <f t="shared" ref="BD18" si="148">(F18-E18)-(F17-E17)</f>
+        <f t="shared" ref="BD18" si="149">(F18-E18)-(F17-E17)</f>
         <v>11.32000000000005</v>
       </c>
       <c r="BE18" s="4">
-        <f t="shared" ref="BE18" si="149">(I18-H18)-(I17-H17)</f>
+        <f t="shared" ref="BE18" si="150">(I18-H18)-(I17-H17)</f>
         <v>0</v>
       </c>
       <c r="BF18" s="4">
-        <f t="shared" ref="BF18" si="150">(L18-K18)-(L17-K17)</f>
+        <f t="shared" ref="BF18" si="151">(L18-K18)-(L17-K17)</f>
         <v>3.75</v>
       </c>
       <c r="BG18" s="4">
-        <f t="shared" ref="BG18" si="151">(O18-N18)-(O17-N17)</f>
+        <f t="shared" ref="BG18" si="152">(O18-N18)-(O17-N17)</f>
         <v>9.2699999999999818</v>
       </c>
       <c r="BH18" s="4">
-        <f t="shared" ref="BH18" si="152">(R18-Q18)-(R17-Q17)</f>
+        <f t="shared" ref="BH18" si="153">(R18-Q18)-(R17-Q17)</f>
         <v>1.6499999999999773</v>
       </c>
       <c r="BI18" s="4">
@@ -4449,11 +4452,11 @@
         <v>0</v>
       </c>
       <c r="BK18" s="4">
-        <f t="shared" ref="BK18" si="153">(AA18-Z18)-(AA17-Z17)</f>
+        <f t="shared" ref="BK18" si="154">(AA18-Z18)-(AA17-Z17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>46234</v>
       </c>
@@ -4464,7 +4467,7 @@
         <v>593.07000000000005</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" ref="D19" si="154">(C19-B19)/B19</f>
+        <f t="shared" ref="D19" si="155">(C19-B19)/B19</f>
         <v>9.8277777777777867E-2</v>
       </c>
       <c r="E19" s="5">
@@ -4474,7 +4477,7 @@
         <v>744.8</v>
       </c>
       <c r="G19" s="11">
-        <f t="shared" ref="G19" si="155">(F19-E19)/E19</f>
+        <f t="shared" ref="G19" si="156">(F19-E19)/E19</f>
         <v>6.3999999999999932E-2</v>
       </c>
       <c r="H19" s="5">
@@ -4484,17 +4487,17 @@
         <v>85.35</v>
       </c>
       <c r="J19" s="12">
-        <f t="shared" ref="J19" si="156">(I19-H19)/H19</f>
+        <f t="shared" ref="J19" si="157">(I19-H19)/H19</f>
         <v>1.8449999999999998</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="21">
         <v>624.35</v>
       </c>
       <c r="L19" s="4">
         <v>666.13</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" ref="M19" si="157">(L19-K19)/K19</f>
+        <f t="shared" ref="M19" si="158">(L19-K19)/K19</f>
         <v>6.6917594298069941E-2</v>
       </c>
       <c r="N19" s="5">
@@ -4504,7 +4507,7 @@
         <v>695.94</v>
       </c>
       <c r="P19" s="12">
-        <f t="shared" ref="P19" si="158">(O19-N19)/N19</f>
+        <f t="shared" ref="P19" si="159">(O19-N19)/N19</f>
         <v>0.12248387096774202</v>
       </c>
       <c r="Q19" s="5">
@@ -4514,7 +4517,7 @@
         <v>669.6</v>
       </c>
       <c r="S19" s="12">
-        <f t="shared" ref="S19" si="159">(R19-Q19)/Q19</f>
+        <f t="shared" ref="S19" si="160">(R19-Q19)/Q19</f>
         <v>9.7704918032786928E-2</v>
       </c>
       <c r="T19" s="5">
@@ -4524,7 +4527,7 @@
         <v>82.1</v>
       </c>
       <c r="V19" s="12">
-        <f>(U19-T19)/T19</f>
+        <f t="shared" si="76"/>
         <v>0.17285714285714276</v>
       </c>
       <c r="W19" s="5">
@@ -4546,36 +4549,36 @@
         <v>0</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" ref="AD19" si="160">A19</f>
+        <f t="shared" ref="AD19" si="161">A19</f>
         <v>46234</v>
       </c>
       <c r="AE19" s="4">
-        <f t="shared" ref="AE19" si="161">B19+E19</f>
+        <f t="shared" ref="AE19" si="162">B19+E19</f>
         <v>1240</v>
       </c>
       <c r="AF19" s="4">
-        <f t="shared" ref="AF19" si="162">AE19-AE18</f>
+        <f t="shared" ref="AF19" si="163">AE19-AE18</f>
         <v>130</v>
       </c>
       <c r="AG19" s="4">
-        <f t="shared" ref="AG19" si="163">C19+F19</f>
+        <f t="shared" ref="AG19" si="164">C19+F19</f>
         <v>1337.87</v>
       </c>
       <c r="AH19" s="4">
-        <f t="shared" ref="AH19" si="164">AG19-AE19</f>
+        <f t="shared" ref="AH19" si="165">AG19-AE19</f>
         <v>97.869999999999891</v>
       </c>
       <c r="AI19" s="13">
-        <f t="shared" ref="AI19" si="165">AH19/AE19</f>
+        <f t="shared" ref="AI19" si="166">AH19/AE19</f>
         <v>7.8927419354838615E-2</v>
       </c>
       <c r="AJ19" s="4">
-        <f t="shared" ref="AJ19" si="166">AH19-AH18</f>
+        <f t="shared" ref="AJ19" si="167">AH19-AH18</f>
         <v>-8.6800000000000637</v>
       </c>
       <c r="AK19" s="10"/>
       <c r="AL19" s="8">
-        <f t="shared" ref="AL19" si="167">A19</f>
+        <f t="shared" ref="AL19" si="168">A19</f>
         <v>46234</v>
       </c>
       <c r="AM19" s="4">
@@ -4583,7 +4586,7 @@
         <v>1954.35</v>
       </c>
       <c r="AN19" s="4">
-        <f t="shared" ref="AN19" si="168">AM19-AM18</f>
+        <f t="shared" ref="AN19" si="169">AM19-AM18</f>
         <v>0</v>
       </c>
       <c r="AO19" s="4">
@@ -4591,72 +4594,72 @@
         <v>2199.12</v>
       </c>
       <c r="AP19" s="4">
-        <f t="shared" ref="AP19" si="169">AO19-AM19</f>
+        <f t="shared" ref="AP19" si="170">AO19-AM19</f>
         <v>244.76999999999998</v>
       </c>
       <c r="AQ19" s="13">
-        <f t="shared" ref="AQ19" si="170">AP19/AM19</f>
+        <f t="shared" ref="AQ19" si="171">AP19/AM19</f>
         <v>0.12524368715941361</v>
       </c>
       <c r="AR19" s="4">
-        <f t="shared" ref="AR19" si="171">AP19-AP18</f>
+        <f t="shared" ref="AR19" si="172">AP19-AP18</f>
         <v>7.2399999999997817</v>
       </c>
       <c r="AS19" s="10"/>
       <c r="AT19" s="8">
-        <f t="shared" ref="AT19" si="172">A19</f>
+        <f t="shared" ref="AT19" si="173">A19</f>
         <v>46234</v>
       </c>
       <c r="AU19" s="4">
-        <f t="shared" ref="AU19" si="173">AE19+AM19</f>
+        <f t="shared" ref="AU19" si="174">AE19+AM19</f>
         <v>3194.35</v>
       </c>
       <c r="AV19" s="4">
-        <f t="shared" ref="AV19" si="174">AU19-AU18</f>
+        <f t="shared" ref="AV19" si="175">AU19-AU18</f>
         <v>130</v>
       </c>
       <c r="AW19" s="4">
-        <f t="shared" ref="AW19" si="175">AG19+AO19</f>
+        <f t="shared" ref="AW19" si="176">AG19+AO19</f>
         <v>3536.99</v>
       </c>
       <c r="AX19" s="4">
-        <f t="shared" ref="AX19" si="176">AW19-AU19</f>
+        <f t="shared" ref="AX19" si="177">AW19-AU19</f>
         <v>342.63999999999987</v>
       </c>
       <c r="AY19" s="13">
-        <f t="shared" ref="AY19" si="177">AX19/AU19</f>
+        <f t="shared" ref="AY19" si="178">AX19/AU19</f>
         <v>0.10726438868627416</v>
       </c>
       <c r="AZ19" s="4">
-        <f t="shared" ref="AZ19" si="178">AX19-AX18</f>
+        <f t="shared" ref="AZ19" si="179">AX19-AX18</f>
         <v>-1.4400000000005093</v>
       </c>
       <c r="BB19" s="8">
-        <f t="shared" ref="BB19" si="179">A19</f>
+        <f t="shared" ref="BB19" si="180">A19</f>
         <v>46234</v>
       </c>
       <c r="BC19" s="4">
-        <f t="shared" ref="BC19" si="180">(C19-B19)-(C18-B18)</f>
+        <f t="shared" ref="BC19" si="181">(C19-B19)-(C18-B18)</f>
         <v>2.2700000000000955</v>
       </c>
       <c r="BD19" s="4">
-        <f t="shared" ref="BD19" si="181">(F19-E19)-(F18-E18)</f>
+        <f t="shared" ref="BD19" si="182">(F19-E19)-(F18-E18)</f>
         <v>-10.950000000000045</v>
       </c>
       <c r="BE19" s="4">
-        <f t="shared" ref="BE19" si="182">(I19-H19)-(I18-H18)</f>
+        <f t="shared" ref="BE19" si="183">(I19-H19)-(I18-H18)</f>
         <v>0</v>
       </c>
       <c r="BF19" s="4">
-        <f t="shared" ref="BF19" si="183">(L19-K19)-(L18-K18)</f>
+        <f t="shared" ref="BF19" si="184">(L19-K19)-(L18-K18)</f>
         <v>2.2400000000000091</v>
       </c>
       <c r="BG19" s="4">
-        <f t="shared" ref="BG19" si="184">(O19-N19)-(O18-N18)</f>
+        <f t="shared" ref="BG19" si="185">(O19-N19)-(O18-N18)</f>
         <v>2.5400000000000773</v>
       </c>
       <c r="BH19" s="4">
-        <f t="shared" ref="BH19" si="185">(R19-Q19)-(R18-Q18)</f>
+        <f t="shared" ref="BH19" si="186">(R19-Q19)-(R18-Q18)</f>
         <v>1.7599999999999909</v>
       </c>
       <c r="BI19" s="4">
@@ -4668,11 +4671,11 @@
         <v>0</v>
       </c>
       <c r="BK19" s="4">
-        <f t="shared" ref="BK19" si="186">(AA19-Z19)-(AA18-Z18)</f>
+        <f t="shared" ref="BK19" si="187">(AA19-Z19)-(AA18-Z18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>46265</v>
       </c>
@@ -4683,7 +4686,7 @@
         <v>637.35</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" ref="D20" si="187">(C20-B20)/B20</f>
+        <f t="shared" ref="D20" si="188">(C20-B20)/B20</f>
         <v>0.11815789473684214</v>
       </c>
       <c r="E20" s="5">
@@ -4693,7 +4696,7 @@
         <v>860.35</v>
       </c>
       <c r="G20" s="11">
-        <f t="shared" ref="G20" si="188">(F20-E20)/E20</f>
+        <f t="shared" ref="G20" si="189">(F20-E20)/E20</f>
         <v>7.5437500000000032E-2</v>
       </c>
       <c r="H20" s="5">
@@ -4703,17 +4706,17 @@
         <v>85.35</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" ref="J20" si="189">(I20-H20)/H20</f>
+        <f t="shared" ref="J20" si="190">(I20-H20)/H20</f>
         <v>1.8449999999999998</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="21">
         <v>623.95000000000005</v>
       </c>
       <c r="L20" s="4">
         <v>666.84</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" ref="M20" si="190">(L20-K20)/K20</f>
+        <f t="shared" ref="M20" si="191">(L20-K20)/K20</f>
         <v>6.8739482330314905E-2</v>
       </c>
       <c r="N20" s="5">
@@ -4723,7 +4726,7 @@
         <v>698.99</v>
       </c>
       <c r="P20" s="12">
-        <f t="shared" ref="P20" si="191">(O20-N20)/N20</f>
+        <f t="shared" ref="P20" si="192">(O20-N20)/N20</f>
         <v>0.12740322580645164</v>
       </c>
       <c r="Q20" s="5">
@@ -4733,7 +4736,7 @@
         <v>678.45</v>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ref="S20" si="192">(R20-Q20)/Q20</f>
+        <f t="shared" ref="S20" si="193">(R20-Q20)/Q20</f>
         <v>0.11221311475409844</v>
       </c>
       <c r="T20" s="5">
@@ -4743,7 +4746,7 @@
         <v>92.67</v>
       </c>
       <c r="V20" s="12">
-        <f>(U20-T20)/T20</f>
+        <f t="shared" si="76"/>
         <v>0.15837500000000002</v>
       </c>
       <c r="W20" s="5">
@@ -4766,36 +4769,36 @@
         <v>0</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" ref="AD20" si="193">A20</f>
+        <f t="shared" ref="AD20" si="194">A20</f>
         <v>46265</v>
       </c>
       <c r="AE20" s="4">
-        <f t="shared" ref="AE20" si="194">B20+E20</f>
+        <f t="shared" ref="AE20" si="195">B20+E20</f>
         <v>1370</v>
       </c>
       <c r="AF20" s="4">
-        <f t="shared" ref="AF20" si="195">AE20-AE19</f>
+        <f t="shared" ref="AF20" si="196">AE20-AE19</f>
         <v>130</v>
       </c>
       <c r="AG20" s="4">
-        <f t="shared" ref="AG20" si="196">C20+F20</f>
+        <f t="shared" ref="AG20" si="197">C20+F20</f>
         <v>1497.7</v>
       </c>
       <c r="AH20" s="4">
-        <f t="shared" ref="AH20" si="197">AG20-AE20</f>
+        <f t="shared" ref="AH20" si="198">AG20-AE20</f>
         <v>127.70000000000005</v>
       </c>
       <c r="AI20" s="13">
-        <f t="shared" ref="AI20" si="198">AH20/AE20</f>
+        <f t="shared" ref="AI20" si="199">AH20/AE20</f>
         <v>9.3211678832116826E-2</v>
       </c>
       <c r="AJ20" s="4">
-        <f t="shared" ref="AJ20" si="199">AH20-AH19</f>
+        <f t="shared" ref="AJ20" si="200">AH20-AH19</f>
         <v>29.830000000000155</v>
       </c>
       <c r="AK20" s="10"/>
       <c r="AL20" s="8">
-        <f t="shared" ref="AL20" si="200">A20</f>
+        <f t="shared" ref="AL20" si="201">A20</f>
         <v>46265</v>
       </c>
       <c r="AM20" s="4">
@@ -4803,7 +4806,7 @@
         <v>2263.9499999999998</v>
       </c>
       <c r="AN20" s="4">
-        <f t="shared" ref="AN20" si="201">AM20-AM19</f>
+        <f t="shared" ref="AN20" si="202">AM20-AM19</f>
         <v>309.59999999999991</v>
       </c>
       <c r="AO20" s="4">
@@ -4811,85 +4814,315 @@
         <v>2523.6000000000004</v>
       </c>
       <c r="AP20" s="4">
-        <f t="shared" ref="AP20" si="202">AO20-AM20</f>
+        <f t="shared" ref="AP20" si="203">AO20-AM20</f>
         <v>259.65000000000055</v>
       </c>
       <c r="AQ20" s="13">
-        <f t="shared" ref="AQ20" si="203">AP20/AM20</f>
+        <f t="shared" ref="AQ20" si="204">AP20/AM20</f>
         <v>0.11468892864241727</v>
       </c>
       <c r="AR20" s="4">
-        <f t="shared" ref="AR20" si="204">AP20-AP19</f>
+        <f t="shared" ref="AR20" si="205">AP20-AP19</f>
         <v>14.880000000000564</v>
       </c>
       <c r="AS20" s="10"/>
       <c r="AT20" s="8">
-        <f t="shared" ref="AT20" si="205">A20</f>
+        <f t="shared" ref="AT20" si="206">A20</f>
         <v>46265</v>
       </c>
       <c r="AU20" s="4">
-        <f t="shared" ref="AU20" si="206">AE20+AM20</f>
+        <f t="shared" ref="AU20" si="207">AE20+AM20</f>
         <v>3633.95</v>
       </c>
       <c r="AV20" s="4">
-        <f t="shared" ref="AV20" si="207">AU20-AU19</f>
+        <f t="shared" ref="AV20" si="208">AU20-AU19</f>
         <v>439.59999999999991</v>
       </c>
       <c r="AW20" s="4">
-        <f t="shared" ref="AW20" si="208">AG20+AO20</f>
+        <f t="shared" ref="AW20" si="209">AG20+AO20</f>
         <v>4021.3</v>
       </c>
       <c r="AX20" s="4">
-        <f t="shared" ref="AX20" si="209">AW20-AU20</f>
+        <f t="shared" ref="AX20" si="210">AW20-AU20</f>
         <v>387.35000000000036</v>
       </c>
       <c r="AY20" s="13">
-        <f t="shared" ref="AY20" si="210">AX20/AU20</f>
+        <f t="shared" ref="AY20" si="211">AX20/AU20</f>
         <v>0.10659200044029235</v>
       </c>
       <c r="AZ20" s="4">
-        <f t="shared" ref="AZ20" si="211">AX20-AX19</f>
+        <f t="shared" ref="AZ20" si="212">AX20-AX19</f>
         <v>44.710000000000491</v>
       </c>
       <c r="BB20" s="8">
-        <f t="shared" ref="BB20" si="212">A20</f>
+        <f t="shared" ref="BB20" si="213">A20</f>
         <v>46265</v>
       </c>
       <c r="BC20" s="4">
-        <f t="shared" ref="BC20" si="213">(C20-B20)-(C19-B19)</f>
+        <f t="shared" ref="BC20" si="214">(C20-B20)-(C19-B19)</f>
         <v>14.279999999999973</v>
       </c>
       <c r="BD20" s="4">
-        <f t="shared" ref="BD20" si="214">(F20-E20)-(F19-E19)</f>
+        <f t="shared" ref="BD20" si="215">(F20-E20)-(F19-E19)</f>
         <v>15.550000000000068</v>
       </c>
       <c r="BE20" s="4">
-        <f t="shared" ref="BE20" si="215">(I20-H20)-(I19-H19)</f>
+        <f t="shared" ref="BE20" si="216">(I20-H20)-(I19-H19)</f>
         <v>0</v>
       </c>
       <c r="BF20" s="4">
-        <f t="shared" ref="BF20" si="216">(L20-K20)-(L19-K19)</f>
+        <f t="shared" ref="BF20" si="217">(L20-K20)-(L19-K19)</f>
         <v>1.1100000000000136</v>
       </c>
       <c r="BG20" s="4">
-        <f t="shared" ref="BG20" si="217">(O20-N20)-(O19-N19)</f>
+        <f t="shared" ref="BG20" si="218">(O20-N20)-(O19-N19)</f>
         <v>3.0499999999999545</v>
       </c>
       <c r="BH20" s="4">
-        <f t="shared" ref="BH20" si="218">(R20-Q20)-(R19-Q19)</f>
+        <f t="shared" ref="BH20" si="219">(R20-Q20)-(R19-Q19)</f>
         <v>8.8500000000000227</v>
       </c>
       <c r="BI20" s="4">
-        <f t="shared" ref="BI20" si="219">(U20-T20)-(U19-T19)</f>
+        <f t="shared" ref="BI20" si="220">(U20-T20)-(U19-T19)</f>
         <v>0.57000000000000739</v>
       </c>
       <c r="BJ20" s="4">
-        <f t="shared" ref="BJ20" si="220">(X20-W20)-(X19-W19)</f>
+        <f t="shared" ref="BJ20" si="221">(X20-W20)-(X19-W19)</f>
         <v>1.3000000000000114</v>
       </c>
       <c r="BK20" s="4">
-        <f t="shared" ref="BK20" si="221">(AA20-Z20)-(AA19-Z19)</f>
-        <v>0</v>
+        <f t="shared" ref="BK20" si="222">(AA20-Z20)-(AA19-Z19)</f>
+        <v>0</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>46295</v>
+      </c>
+      <c r="B21" s="5">
+        <v>600</v>
+      </c>
+      <c r="C21" s="4">
+        <v>660.22</v>
+      </c>
+      <c r="D21" s="11">
+        <f t="shared" ref="D21" si="223">(C21-B21)/B21</f>
+        <v>0.10036666666666672</v>
+      </c>
+      <c r="E21" s="5">
+        <v>900</v>
+      </c>
+      <c r="F21" s="4">
+        <v>974.4</v>
+      </c>
+      <c r="G21" s="11">
+        <f t="shared" ref="G21" si="224">(F21-E21)/E21</f>
+        <v>8.2666666666666638E-2</v>
+      </c>
+      <c r="H21" s="5">
+        <v>30</v>
+      </c>
+      <c r="I21" s="4">
+        <v>85.35</v>
+      </c>
+      <c r="J21" s="12">
+        <f t="shared" ref="J21" si="225">(I21-H21)/H21</f>
+        <v>1.8449999999999998</v>
+      </c>
+      <c r="K21" s="21">
+        <v>623.95000000000005</v>
+      </c>
+      <c r="L21" s="4">
+        <v>674.58</v>
+      </c>
+      <c r="M21" s="12">
+        <f t="shared" ref="M21" si="226">(L21-K21)/K21</f>
+        <v>8.1144322461735696E-2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>620</v>
+      </c>
+      <c r="O21" s="4">
+        <v>704.91</v>
+      </c>
+      <c r="P21" s="12">
+        <f t="shared" ref="P21" si="227">(O21-N21)/N21</f>
+        <v>0.13695161290322574</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>610</v>
+      </c>
+      <c r="R21" s="4">
+        <v>687.59</v>
+      </c>
+      <c r="S21" s="12">
+        <f t="shared" ref="S21" si="228">(R21-Q21)/Q21</f>
+        <v>0.12719672131147547</v>
+      </c>
+      <c r="T21" s="5">
+        <v>80</v>
+      </c>
+      <c r="U21" s="4">
+        <v>93.44</v>
+      </c>
+      <c r="V21" s="12">
+        <f t="shared" si="76"/>
+        <v>0.16799999999999998</v>
+      </c>
+      <c r="W21" s="5">
+        <v>200</v>
+      </c>
+      <c r="X21" s="4">
+        <v>203.05</v>
+      </c>
+      <c r="Y21" s="12">
+        <f>(X21-W21)/W21</f>
+        <v>1.5250000000000057E-2</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="4">
+        <v>100.59</v>
+      </c>
+      <c r="AB21" s="12">
+        <f>(AA21-Z21)/Z21</f>
+        <v>5.9000000000000337E-3</v>
+      </c>
+      <c r="AD21" s="8">
+        <f t="shared" ref="AD21" si="229">A21</f>
+        <v>46295</v>
+      </c>
+      <c r="AE21" s="4">
+        <f t="shared" ref="AE21" si="230">B21+E21</f>
+        <v>1500</v>
+      </c>
+      <c r="AF21" s="4">
+        <f t="shared" ref="AF21" si="231">AE21-AE20</f>
+        <v>130</v>
+      </c>
+      <c r="AG21" s="4">
+        <f t="shared" ref="AG21" si="232">C21+F21</f>
+        <v>1634.62</v>
+      </c>
+      <c r="AH21" s="4">
+        <f t="shared" ref="AH21" si="233">AG21-AE21</f>
+        <v>134.61999999999989</v>
+      </c>
+      <c r="AI21" s="13">
+        <f t="shared" ref="AI21" si="234">AH21/AE21</f>
+        <v>8.97466666666666E-2</v>
+      </c>
+      <c r="AJ21" s="4">
+        <f t="shared" ref="AJ21" si="235">AH21-AH20</f>
+        <v>6.9199999999998454</v>
+      </c>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="8">
+        <f t="shared" ref="AL21" si="236">A21</f>
+        <v>46295</v>
+      </c>
+      <c r="AM21" s="4">
+        <f>H21+K21+N21+Q21+T21+W21+Z21</f>
+        <v>2263.9499999999998</v>
+      </c>
+      <c r="AN21" s="4">
+        <f t="shared" ref="AN21" si="237">AM21-AM20</f>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="4">
+        <f>I21+L21+O21+R21+U21+X21+AA21</f>
+        <v>2549.5100000000007</v>
+      </c>
+      <c r="AP21" s="4">
+        <f t="shared" ref="AP21" si="238">AO21-AM21</f>
+        <v>285.56000000000085</v>
+      </c>
+      <c r="AQ21" s="13">
+        <f t="shared" ref="AQ21" si="239">AP21/AM21</f>
+        <v>0.12613352768391567</v>
+      </c>
+      <c r="AR21" s="4">
+        <f t="shared" ref="AR21" si="240">AP21-AP20</f>
+        <v>25.910000000000309</v>
+      </c>
+      <c r="AS21" s="10"/>
+      <c r="AT21" s="8">
+        <f t="shared" ref="AT21" si="241">A21</f>
+        <v>46295</v>
+      </c>
+      <c r="AU21" s="4">
+        <f t="shared" ref="AU21" si="242">AE21+AM21</f>
+        <v>3763.95</v>
+      </c>
+      <c r="AV21" s="4">
+        <f t="shared" ref="AV21" si="243">AU21-AU20</f>
+        <v>130</v>
+      </c>
+      <c r="AW21" s="4">
+        <f t="shared" ref="AW21" si="244">AG21+AO21</f>
+        <v>4184.130000000001</v>
+      </c>
+      <c r="AX21" s="4">
+        <f t="shared" ref="AX21" si="245">AW21-AU21</f>
+        <v>420.1800000000012</v>
+      </c>
+      <c r="AY21" s="13">
+        <f t="shared" ref="AY21" si="246">AX21/AU21</f>
+        <v>0.11163272625831938</v>
+      </c>
+      <c r="AZ21" s="4">
+        <f t="shared" ref="AZ21" si="247">AX21-AX20</f>
+        <v>32.830000000000837</v>
+      </c>
+      <c r="BB21" s="8">
+        <f t="shared" ref="BB21" si="248">A21</f>
+        <v>46295</v>
+      </c>
+      <c r="BC21" s="4">
+        <f t="shared" ref="BC21" si="249">(C21-B21)-(C20-B20)</f>
+        <v>-7.1299999999999955</v>
+      </c>
+      <c r="BD21" s="4">
+        <f t="shared" ref="BD21" si="250">(F21-E21)-(F20-E20)</f>
+        <v>14.049999999999955</v>
+      </c>
+      <c r="BE21" s="4">
+        <f t="shared" ref="BE21" si="251">(I21-H21)-(I20-H20)</f>
+        <v>0</v>
+      </c>
+      <c r="BF21" s="4">
+        <f t="shared" ref="BF21" si="252">(L21-K21)-(L20-K20)</f>
+        <v>7.7400000000000091</v>
+      </c>
+      <c r="BG21" s="4">
+        <f t="shared" ref="BG21" si="253">(O21-N21)-(O20-N20)</f>
+        <v>5.9199999999999591</v>
+      </c>
+      <c r="BH21" s="4">
+        <f t="shared" ref="BH21" si="254">(R21-Q21)-(R20-Q20)</f>
+        <v>9.1399999999999864</v>
+      </c>
+      <c r="BI21" s="4">
+        <f t="shared" ref="BI21" si="255">(U21-T21)-(U20-T20)</f>
+        <v>0.76999999999999602</v>
+      </c>
+      <c r="BJ21" s="4">
+        <f t="shared" ref="BJ21" si="256">(X21-W21)-(X20-W20)</f>
+        <v>1.75</v>
+      </c>
+      <c r="BK21" s="4">
+        <f t="shared" ref="BK21" si="257">(AA21-Z21)-(AA20-Z20)</f>
+        <v>0.59000000000000341</v>
+      </c>
+      <c r="BN21">
+        <v>20</v>
+      </c>
+      <c r="BO21">
+        <v>20.05</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Investavimas Rima.xlsx
+++ b/excel/Investavimas Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81414D25-56C4-4E11-BE5D-E27F1E97A215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6581A8F-7EAC-4F3D-9925-DCD5BCB07754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2090,10 +2090,10 @@
         <v>1.835</v>
       </c>
       <c r="K8" s="21">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L8" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" ref="M8:M11" si="35">(L8-K8)/K8</f>
@@ -2181,15 +2181,15 @@
       </c>
       <c r="AM8" s="4">
         <f t="shared" si="3"/>
-        <v>840</v>
+        <v>640</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="28"/>
-        <v>810</v>
+        <v>610</v>
       </c>
       <c r="AO8" s="4">
         <f t="shared" si="4"/>
-        <v>915.05</v>
+        <v>715.05</v>
       </c>
       <c r="AP8" s="4">
         <f t="shared" si="5"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AQ8" s="13">
         <f t="shared" si="6"/>
-        <v>8.9345238095238047E-2</v>
+        <v>0.11726562499999993</v>
       </c>
       <c r="AR8" s="4">
         <f t="shared" si="29"/>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="AU8" s="4">
         <f t="shared" si="18"/>
-        <v>1050</v>
+        <v>850</v>
       </c>
       <c r="AV8" s="4">
         <f t="shared" si="30"/>
-        <v>840</v>
+        <v>640</v>
       </c>
       <c r="AW8" s="4">
         <f t="shared" si="19"/>
-        <v>1129.6799999999998</v>
+        <v>929.68</v>
       </c>
       <c r="AX8" s="4">
         <f t="shared" si="7"/>
-        <v>79.679999999999836</v>
+        <v>79.67999999999995</v>
       </c>
       <c r="AY8" s="13">
         <f t="shared" si="8"/>
-        <v>7.5885714285714126E-2</v>
+        <v>9.3741176470588175E-2</v>
       </c>
       <c r="AZ8" s="4">
         <f t="shared" si="31"/>
-        <v>20.529999999999859</v>
+        <v>20.529999999999973</v>
       </c>
       <c r="BB8" s="8">
         <f t="shared" si="9"/>
@@ -2307,10 +2307,10 @@
         <v>1.835</v>
       </c>
       <c r="K9" s="21">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L9" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="35"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AM9" s="4">
         <f t="shared" si="3"/>
-        <v>1440</v>
+        <v>1240</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="28"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AO9" s="4">
         <f t="shared" si="4"/>
-        <v>1518.75</v>
+        <v>1318.75</v>
       </c>
       <c r="AP9" s="4">
         <f t="shared" si="5"/>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="AQ9" s="13">
         <f t="shared" si="6"/>
-        <v>5.46875E-2</v>
+        <v>6.3508064516129031E-2</v>
       </c>
       <c r="AR9" s="4">
         <f t="shared" si="29"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AU9" s="4">
         <f t="shared" si="18"/>
-        <v>1680</v>
+        <v>1480</v>
       </c>
       <c r="AV9" s="4">
         <f t="shared" si="30"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AW9" s="4">
         <f t="shared" si="19"/>
-        <v>1764.76</v>
+        <v>1564.76</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" si="7"/>
@@ -2444,11 +2444,11 @@
       </c>
       <c r="AY9" s="13">
         <f t="shared" si="8"/>
-        <v>5.045238095238095E-2</v>
+        <v>5.7270270270270263E-2</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="31"/>
-        <v>5.0800000000001546</v>
+        <v>5.0800000000000409</v>
       </c>
       <c r="BB9" s="8">
         <f t="shared" si="9"/>
@@ -2525,10 +2525,10 @@
         <v>1.835</v>
       </c>
       <c r="K10" s="21">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L10" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="35"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AM10" s="4">
         <f t="shared" si="3"/>
-        <v>1460</v>
+        <v>1260</v>
       </c>
       <c r="AN10" s="4">
         <f t="shared" si="28"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AO10" s="4">
         <f t="shared" si="4"/>
-        <v>1570.02</v>
+        <v>1370.02</v>
       </c>
       <c r="AP10" s="4">
         <f t="shared" si="5"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AQ10" s="13">
         <f t="shared" si="6"/>
-        <v>7.535616438356163E-2</v>
+        <v>8.7317460317460308E-2</v>
       </c>
       <c r="AR10" s="4">
         <f t="shared" si="29"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AU10" s="4">
         <f t="shared" si="18"/>
-        <v>1730</v>
+        <v>1530</v>
       </c>
       <c r="AV10" s="4">
         <f t="shared" si="30"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AW10" s="4">
         <f t="shared" si="19"/>
-        <v>1854.76</v>
+        <v>1654.76</v>
       </c>
       <c r="AX10" s="4">
         <f t="shared" si="7"/>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AY10" s="13">
         <f t="shared" si="8"/>
-        <v>7.2115606936416179E-2</v>
+        <v>8.1542483660130713E-2</v>
       </c>
       <c r="AZ10" s="4">
         <f t="shared" si="31"/>
@@ -2743,14 +2743,14 @@
         <v>1.835</v>
       </c>
       <c r="K11" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L11" s="4">
-        <v>525</v>
+        <v>325</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="35"/>
-        <v>0.05</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="N11" s="5">
         <v>420</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AM11" s="4">
         <f t="shared" si="3"/>
-        <v>1560</v>
+        <v>1360</v>
       </c>
       <c r="AN11" s="4">
         <f t="shared" si="28"/>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AO11" s="4">
         <f t="shared" si="4"/>
-        <v>1700.19</v>
+        <v>1500.19</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" si="5"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AQ11" s="13">
         <f t="shared" si="6"/>
-        <v>8.9865384615384653E-2</v>
+        <v>0.10308088235294122</v>
       </c>
       <c r="AR11" s="4">
         <f t="shared" si="29"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AU11" s="4">
         <f t="shared" si="18"/>
-        <v>1860</v>
+        <v>1660</v>
       </c>
       <c r="AV11" s="4">
         <f t="shared" si="30"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AW11" s="4">
         <f t="shared" si="19"/>
-        <v>2013.3000000000002</v>
+        <v>1813.3000000000002</v>
       </c>
       <c r="AX11" s="4">
         <f t="shared" si="7"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AY11" s="13">
         <f t="shared" si="8"/>
-        <v>8.2419354838709769E-2</v>
+        <v>9.2349397590361551E-2</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" si="31"/>
@@ -2961,14 +2961,14 @@
         <v>1.8366666666666664</v>
       </c>
       <c r="K12" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L12" s="4">
-        <v>537.22</v>
+        <v>331.12</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" ref="M12" si="39">(L12-K12)/K12</f>
-        <v>7.4440000000000048E-2</v>
+        <v>0.10373333333333334</v>
       </c>
       <c r="N12" s="5">
         <v>420</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AM12" s="4">
         <f t="shared" si="3"/>
-        <v>1560</v>
+        <v>1360</v>
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="28"/>
@@ -3060,19 +3060,19 @@
       </c>
       <c r="AO12" s="4">
         <f t="shared" si="4"/>
-        <v>1716.71</v>
+        <v>1510.6100000000001</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="5"/>
-        <v>156.71000000000004</v>
+        <v>150.61000000000013</v>
       </c>
       <c r="AQ12" s="13">
         <f t="shared" si="6"/>
-        <v>0.10045512820512822</v>
+        <v>0.11074264705882363</v>
       </c>
       <c r="AR12" s="4">
         <f t="shared" si="29"/>
-        <v>16.519999999999982</v>
+        <v>10.420000000000073</v>
       </c>
       <c r="AS12" s="10"/>
       <c r="AT12" s="8">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="18"/>
-        <v>1860</v>
+        <v>1660</v>
       </c>
       <c r="AV12" s="4">
         <f t="shared" si="30"/>
@@ -3089,19 +3089,19 @@
       </c>
       <c r="AW12" s="4">
         <f t="shared" si="19"/>
-        <v>2034.56</v>
+        <v>1828.46</v>
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="7"/>
-        <v>174.55999999999995</v>
+        <v>168.46000000000004</v>
       </c>
       <c r="AY12" s="13">
         <f t="shared" si="8"/>
-        <v>9.3849462365591371E-2</v>
+        <v>0.1014819277108434</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="31"/>
-        <v>21.259999999999764</v>
+        <v>15.159999999999854</v>
       </c>
       <c r="BB12" s="8">
         <f t="shared" si="9"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BF12" s="4">
         <f t="shared" si="23"/>
-        <v>12.220000000000027</v>
+        <v>6.1200000000000045</v>
       </c>
       <c r="BG12" s="4">
         <f t="shared" si="24"/>
@@ -3180,14 +3180,14 @@
         <v>1.8366666666666664</v>
       </c>
       <c r="K13" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L13" s="4">
-        <v>537.22</v>
+        <v>331.12</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" ref="M13" si="44">(L13-K13)/K13</f>
-        <v>7.4440000000000048E-2</v>
+        <v>0.10373333333333334</v>
       </c>
       <c r="N13" s="5">
         <v>420</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AM13" s="4">
         <f t="shared" si="3"/>
-        <v>1560</v>
+        <v>1360</v>
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="28"/>
@@ -3279,15 +3279,15 @@
       </c>
       <c r="AO13" s="4">
         <f t="shared" si="4"/>
-        <v>1721.08</v>
+        <v>1514.98</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="5"/>
-        <v>161.07999999999993</v>
+        <v>154.98000000000002</v>
       </c>
       <c r="AQ13" s="13">
         <f t="shared" si="6"/>
-        <v>0.10325641025641021</v>
+        <v>0.11395588235294118</v>
       </c>
       <c r="AR13" s="4">
         <f t="shared" si="29"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="18"/>
-        <v>2020</v>
+        <v>1820</v>
       </c>
       <c r="AV13" s="4">
         <f t="shared" si="30"/>
@@ -3308,19 +3308,19 @@
       </c>
       <c r="AW13" s="4">
         <f t="shared" si="19"/>
-        <v>2206.5299999999997</v>
+        <v>2000.43</v>
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="7"/>
-        <v>186.52999999999975</v>
+        <v>180.43000000000006</v>
       </c>
       <c r="AY13" s="13">
         <f t="shared" si="8"/>
-        <v>9.2341584158415715E-2</v>
+        <v>9.9137362637362669E-2</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="31"/>
-        <v>11.9699999999998</v>
+        <v>11.970000000000027</v>
       </c>
       <c r="BB13" s="8">
         <f t="shared" si="9"/>
@@ -3398,14 +3398,14 @@
         <v>1.8366666666666664</v>
       </c>
       <c r="K14" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L14" s="4">
-        <v>537.22</v>
+        <v>331.12</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" ref="M14" si="50">(L14-K14)/K14</f>
-        <v>7.4440000000000048E-2</v>
+        <v>0.10373333333333334</v>
       </c>
       <c r="N14" s="5">
         <v>420</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AM14" s="4">
         <f t="shared" si="3"/>
-        <v>1560</v>
+        <v>1360</v>
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="28"/>
@@ -3497,15 +3497,15 @@
       </c>
       <c r="AO14" s="4">
         <f t="shared" si="4"/>
-        <v>1736.15</v>
+        <v>1530.0500000000002</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="5"/>
-        <v>176.15000000000009</v>
+        <v>170.05000000000018</v>
       </c>
       <c r="AQ14" s="13">
         <f t="shared" si="6"/>
-        <v>0.11291666666666672</v>
+        <v>0.12503676470588249</v>
       </c>
       <c r="AR14" s="4">
         <f t="shared" si="29"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="18"/>
-        <v>2150</v>
+        <v>1950</v>
       </c>
       <c r="AV14" s="4">
         <f t="shared" si="30"/>
@@ -3526,19 +3526,19 @@
       </c>
       <c r="AW14" s="4">
         <f t="shared" si="19"/>
-        <v>2358.63</v>
+        <v>2152.5300000000002</v>
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="7"/>
-        <v>208.63000000000011</v>
+        <v>202.5300000000002</v>
       </c>
       <c r="AY14" s="13">
         <f t="shared" si="8"/>
-        <v>9.7037209302325636E-2</v>
+        <v>0.10386153846153856</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="31"/>
-        <v>22.100000000000364</v>
+        <v>22.100000000000136</v>
       </c>
       <c r="BB14" s="8">
         <f t="shared" si="9"/>
@@ -3616,14 +3616,14 @@
         <v>1.8366666666666664</v>
       </c>
       <c r="K15" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L15" s="4">
-        <v>544.55999999999995</v>
+        <v>336.24</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" ref="M15" si="56">(L15-K15)/K15</f>
-        <v>8.9119999999999894E-2</v>
+        <v>0.12080000000000003</v>
       </c>
       <c r="N15" s="5">
         <v>620</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="AM15" s="4">
         <f t="shared" si="3"/>
-        <v>1760</v>
+        <v>1560</v>
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="28"/>
@@ -3715,19 +3715,19 @@
       </c>
       <c r="AO15" s="4">
         <f t="shared" si="4"/>
-        <v>1971.55</v>
+        <v>1763.23</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="5"/>
-        <v>211.54999999999995</v>
+        <v>203.23000000000002</v>
       </c>
       <c r="AQ15" s="13">
         <f t="shared" si="6"/>
-        <v>0.1201988636363636</v>
+        <v>0.13027564102564104</v>
       </c>
       <c r="AR15" s="4">
         <f t="shared" si="29"/>
-        <v>35.399999999999864</v>
+        <v>33.179999999999836</v>
       </c>
       <c r="AS15" s="10"/>
       <c r="AT15" s="8">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="18"/>
-        <v>2480</v>
+        <v>2280</v>
       </c>
       <c r="AV15" s="4">
         <f t="shared" si="30"/>
@@ -3744,19 +3744,19 @@
       </c>
       <c r="AW15" s="4">
         <f t="shared" si="19"/>
-        <v>2682.46</v>
+        <v>2474.1400000000003</v>
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="7"/>
-        <v>202.46000000000004</v>
+        <v>194.14000000000033</v>
       </c>
       <c r="AY15" s="13">
         <f t="shared" si="8"/>
-        <v>8.1637096774193563E-2</v>
+        <v>8.5149122807017683E-2</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="31"/>
-        <v>-6.1700000000000728</v>
+        <v>-8.3899999999998727</v>
       </c>
       <c r="BB15" s="8">
         <f t="shared" ref="BB15" si="63">A15</f>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="BF15" s="4">
         <f t="shared" ref="BF15" si="67">(L15-K15)-(L14-K14)</f>
-        <v>7.3399999999999181</v>
+        <v>5.1200000000000045</v>
       </c>
       <c r="BG15" s="4">
         <f t="shared" ref="BG15" si="68">(O15-N15)-(O14-N14)</f>
@@ -3834,14 +3834,14 @@
         <v>1.8366666666666664</v>
       </c>
       <c r="K16" s="21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L16" s="4">
-        <v>549.24</v>
+        <v>338.58</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" ref="M16" si="73">(L16-K16)/K16</f>
-        <v>9.8480000000000012E-2</v>
+        <v>0.12859999999999994</v>
       </c>
       <c r="N16" s="5">
         <v>620</v>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AM16" s="4">
         <f t="shared" si="3"/>
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="28"/>
@@ -3934,19 +3934,19 @@
       </c>
       <c r="AO16" s="4">
         <f t="shared" si="4"/>
-        <v>2028.74</v>
+        <v>1818.0799999999997</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="5"/>
-        <v>228.74</v>
+        <v>218.0799999999997</v>
       </c>
       <c r="AQ16" s="13">
         <f t="shared" si="6"/>
-        <v>0.12707777777777779</v>
+        <v>0.13629999999999981</v>
       </c>
       <c r="AR16" s="4">
         <f t="shared" si="29"/>
-        <v>17.190000000000055</v>
+        <v>14.849999999999682</v>
       </c>
       <c r="AS16" s="10"/>
       <c r="AT16" s="8">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="18"/>
-        <v>2650</v>
+        <v>2450</v>
       </c>
       <c r="AV16" s="4">
         <f t="shared" si="30"/>
@@ -3963,19 +3963,19 @@
       </c>
       <c r="AW16" s="4">
         <f t="shared" si="19"/>
-        <v>2923.3599999999997</v>
+        <v>2712.7</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="7"/>
-        <v>273.35999999999967</v>
+        <v>262.69999999999982</v>
       </c>
       <c r="AY16" s="13">
         <f t="shared" si="8"/>
-        <v>0.10315471698113195</v>
+        <v>0.1072244897959183</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="31"/>
-        <v>70.899999999999636</v>
+        <v>68.559999999999491</v>
       </c>
       <c r="BB16" s="8">
         <f t="shared" ref="BB16" si="81">A16</f>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="BF16" s="4">
         <f t="shared" ref="BF16" si="85">(L16-K16)-(L15-K15)</f>
-        <v>4.6800000000000637</v>
+        <v>2.339999999999975</v>
       </c>
       <c r="BG16" s="4">
         <f t="shared" ref="BG16" si="86">(O16-N16)-(O15-N15)</f>
@@ -4053,14 +4053,14 @@
         <v>1.8449999999999998</v>
       </c>
       <c r="K17" s="21">
-        <v>515.39</v>
+        <v>514.99</v>
       </c>
       <c r="L17" s="4">
-        <v>551.17999999999995</v>
+        <v>554.53</v>
       </c>
       <c r="M17" s="12">
         <f t="shared" ref="M17" si="92">(L17-K17)/K17</f>
-        <v>6.9442558062826135E-2</v>
+        <v>7.6778189867764357E-2</v>
       </c>
       <c r="N17" s="5">
         <v>620</v>
@@ -4145,27 +4145,27 @@
       </c>
       <c r="AM17" s="4">
         <f t="shared" si="3"/>
-        <v>1845.3899999999999</v>
+        <v>1844.99</v>
       </c>
       <c r="AN17" s="4">
         <f t="shared" ref="AN17" si="103">AM17-AM16</f>
-        <v>45.389999999999873</v>
+        <v>244.99</v>
       </c>
       <c r="AO17" s="4">
         <f t="shared" si="4"/>
-        <v>2067.35</v>
+        <v>2070.6999999999998</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" ref="AP17" si="104">AO17-AM17</f>
-        <v>221.96000000000004</v>
+        <v>225.70999999999981</v>
       </c>
       <c r="AQ17" s="13">
         <f t="shared" ref="AQ17" si="105">AP17/AM17</f>
-        <v>0.12027809839654494</v>
+        <v>0.12233670643201308</v>
       </c>
       <c r="AR17" s="4">
         <f t="shared" ref="AR17" si="106">AP17-AP16</f>
-        <v>-6.7799999999999727</v>
+        <v>7.6300000000001091</v>
       </c>
       <c r="AS17" s="10"/>
       <c r="AT17" s="8">
@@ -4174,27 +4174,27 @@
       </c>
       <c r="AU17" s="4">
         <f t="shared" ref="AU17" si="108">AE17+AM17</f>
-        <v>2825.39</v>
+        <v>2824.99</v>
       </c>
       <c r="AV17" s="4">
         <f t="shared" ref="AV17" si="109">AU17-AU16</f>
-        <v>175.38999999999987</v>
+        <v>374.98999999999978</v>
       </c>
       <c r="AW17" s="4">
         <f t="shared" ref="AW17" si="110">AG17+AO17</f>
-        <v>3138.85</v>
+        <v>3142.2</v>
       </c>
       <c r="AX17" s="4">
         <f t="shared" ref="AX17" si="111">AW17-AU17</f>
-        <v>313.46000000000004</v>
+        <v>317.21000000000004</v>
       </c>
       <c r="AY17" s="13">
         <f t="shared" ref="AY17" si="112">AX17/AU17</f>
-        <v>0.1109439758758968</v>
+        <v>0.11228712314025893</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" ref="AZ17" si="113">AX17-AX16</f>
-        <v>40.100000000000364</v>
+        <v>54.510000000000218</v>
       </c>
       <c r="BB17" s="8">
         <f t="shared" ref="BB17" si="114">A17</f>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BF17" s="4">
         <f t="shared" ref="BF17" si="118">(L17-K17)-(L16-K16)</f>
-        <v>-13.450000000000045</v>
+        <v>0.95999999999997954</v>
       </c>
       <c r="BG17" s="4">
         <f t="shared" ref="BG17" si="119">(O17-N17)-(O16-N16)</f>
@@ -4272,14 +4272,14 @@
         <v>1.8449999999999998</v>
       </c>
       <c r="K18" s="21">
-        <v>624.35</v>
+        <v>623.95000000000005</v>
       </c>
       <c r="L18" s="4">
-        <v>663.89</v>
+        <v>663.49</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" ref="M18" si="125">(L18-K18)/K18</f>
-        <v>6.3329863057579816E-2</v>
+        <v>6.3370462376792946E-2</v>
       </c>
       <c r="N18" s="5">
         <v>620</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AM18" s="4">
         <f t="shared" si="3"/>
-        <v>1954.35</v>
+        <v>1953.95</v>
       </c>
       <c r="AN18" s="4">
         <f t="shared" ref="AN18" si="136">AM18-AM17</f>
@@ -4372,19 +4372,19 @@
       </c>
       <c r="AO18" s="4">
         <f t="shared" si="4"/>
-        <v>2191.88</v>
+        <v>2191.48</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" ref="AP18" si="137">AO18-AM18</f>
-        <v>237.5300000000002</v>
+        <v>237.52999999999997</v>
       </c>
       <c r="AQ18" s="13">
         <f t="shared" ref="AQ18" si="138">AP18/AM18</f>
-        <v>0.12153913065725187</v>
+        <v>0.12156401136160085</v>
       </c>
       <c r="AR18" s="4">
         <f t="shared" ref="AR18" si="139">AP18-AP17</f>
-        <v>15.570000000000164</v>
+        <v>11.820000000000164</v>
       </c>
       <c r="AS18" s="10"/>
       <c r="AT18" s="8">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AU18" s="4">
         <f t="shared" ref="AU18" si="141">AE18+AM18</f>
-        <v>3064.35</v>
+        <v>3063.95</v>
       </c>
       <c r="AV18" s="4">
         <f t="shared" ref="AV18" si="142">AU18-AU17</f>
@@ -4401,19 +4401,19 @@
       </c>
       <c r="AW18" s="4">
         <f t="shared" ref="AW18" si="143">AG18+AO18</f>
-        <v>3408.4300000000003</v>
+        <v>3408.0299999999997</v>
       </c>
       <c r="AX18" s="4">
         <f t="shared" ref="AX18" si="144">AW18-AU18</f>
-        <v>344.08000000000038</v>
+        <v>344.07999999999993</v>
       </c>
       <c r="AY18" s="13">
         <f t="shared" ref="AY18" si="145">AX18/AU18</f>
-        <v>0.11228482386150419</v>
+        <v>0.11229948269390817</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" ref="AZ18" si="146">AX18-AX17</f>
-        <v>30.620000000000346</v>
+        <v>26.869999999999891</v>
       </c>
       <c r="BB18" s="8">
         <f t="shared" ref="BB18" si="147">A18</f>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="BF18" s="4">
         <f t="shared" ref="BF18" si="151">(L18-K18)-(L17-K17)</f>
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BG18" s="4">
         <f t="shared" ref="BG18" si="152">(O18-N18)-(O17-N17)</f>
@@ -4491,14 +4491,14 @@
         <v>1.8449999999999998</v>
       </c>
       <c r="K19" s="21">
-        <v>624.35</v>
+        <v>623.95000000000005</v>
       </c>
       <c r="L19" s="4">
-        <v>666.13</v>
+        <v>665.73</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" ref="M19" si="158">(L19-K19)/K19</f>
-        <v>6.6917594298069941E-2</v>
+        <v>6.6960493629297166E-2</v>
       </c>
       <c r="N19" s="5">
         <v>620</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM19" s="4">
         <f>H19+K19+N19+Q19+T19+W19+Z19</f>
-        <v>1954.35</v>
+        <v>1953.95</v>
       </c>
       <c r="AN19" s="4">
         <f t="shared" ref="AN19" si="169">AM19-AM18</f>
@@ -4591,15 +4591,15 @@
       </c>
       <c r="AO19" s="4">
         <f>I19+L19+O19+R19+U19+X19+AA19</f>
-        <v>2199.12</v>
+        <v>2198.7199999999998</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" ref="AP19" si="170">AO19-AM19</f>
-        <v>244.76999999999998</v>
+        <v>244.76999999999975</v>
       </c>
       <c r="AQ19" s="13">
         <f t="shared" ref="AQ19" si="171">AP19/AM19</f>
-        <v>0.12524368715941361</v>
+        <v>0.12526932623659753</v>
       </c>
       <c r="AR19" s="4">
         <f t="shared" ref="AR19" si="172">AP19-AP18</f>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AU19" s="4">
         <f t="shared" ref="AU19" si="174">AE19+AM19</f>
-        <v>3194.35</v>
+        <v>3193.95</v>
       </c>
       <c r="AV19" s="4">
         <f t="shared" ref="AV19" si="175">AU19-AU18</f>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AW19" s="4">
         <f t="shared" ref="AW19" si="176">AG19+AO19</f>
-        <v>3536.99</v>
+        <v>3536.5899999999997</v>
       </c>
       <c r="AX19" s="4">
         <f t="shared" ref="AX19" si="177">AW19-AU19</f>
@@ -4628,11 +4628,11 @@
       </c>
       <c r="AY19" s="13">
         <f t="shared" ref="AY19" si="178">AX19/AU19</f>
-        <v>0.10726438868627416</v>
+        <v>0.10727782213246917</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" ref="AZ19" si="179">AX19-AX18</f>
-        <v>-1.4400000000005093</v>
+        <v>-1.4400000000000546</v>
       </c>
       <c r="BB19" s="8">
         <f t="shared" ref="BB19" si="180">A19</f>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" ref="AN20" si="202">AM20-AM19</f>
-        <v>309.59999999999991</v>
+        <v>309.99999999999977</v>
       </c>
       <c r="AO20" s="4">
         <f>I20+L20+O20+R20+U20+X20+AA20</f>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AR20" s="4">
         <f t="shared" ref="AR20" si="205">AP20-AP19</f>
-        <v>14.880000000000564</v>
+        <v>14.880000000000791</v>
       </c>
       <c r="AS20" s="10"/>
       <c r="AT20" s="8">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AV20" s="4">
         <f t="shared" ref="AV20" si="208">AU20-AU19</f>
-        <v>439.59999999999991</v>
+        <v>440</v>
       </c>
       <c r="AW20" s="4">
         <f t="shared" ref="AW20" si="209">AG20+AO20</f>

--- a/excel/Investavimas Rima.xlsx
+++ b/excel/Investavimas Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6581A8F-7EAC-4F3D-9925-DCD5BCB07754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228EB3BC-823C-4A07-8EC4-DE0A9DDEA3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="5">
-        <v>410</v>
+        <v>205</v>
       </c>
       <c r="R8" s="4">
-        <v>430</v>
+        <v>215</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" ref="S8:S12" si="36">(R8-Q8)/Q8</f>
@@ -2181,27 +2181,27 @@
       </c>
       <c r="AM8" s="4">
         <f t="shared" si="3"/>
-        <v>640</v>
+        <v>435</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="28"/>
-        <v>610</v>
+        <v>405</v>
       </c>
       <c r="AO8" s="4">
         <f t="shared" si="4"/>
-        <v>715.05</v>
+        <v>500.05</v>
       </c>
       <c r="AP8" s="4">
         <f t="shared" si="5"/>
-        <v>75.049999999999955</v>
+        <v>65.050000000000011</v>
       </c>
       <c r="AQ8" s="13">
         <f t="shared" si="6"/>
-        <v>0.11726562499999993</v>
+        <v>0.1495402298850575</v>
       </c>
       <c r="AR8" s="4">
         <f t="shared" si="29"/>
-        <v>19.999999999999957</v>
+        <v>10.000000000000014</v>
       </c>
       <c r="AS8" s="10"/>
       <c r="AT8" s="8">
@@ -2210,27 +2210,27 @@
       </c>
       <c r="AU8" s="4">
         <f t="shared" si="18"/>
-        <v>850</v>
+        <v>645</v>
       </c>
       <c r="AV8" s="4">
         <f t="shared" si="30"/>
-        <v>640</v>
+        <v>435</v>
       </c>
       <c r="AW8" s="4">
         <f t="shared" si="19"/>
-        <v>929.68</v>
+        <v>714.68000000000006</v>
       </c>
       <c r="AX8" s="4">
         <f t="shared" si="7"/>
-        <v>79.67999999999995</v>
+        <v>69.680000000000064</v>
       </c>
       <c r="AY8" s="13">
         <f t="shared" si="8"/>
-        <v>9.3741176470588175E-2</v>
+        <v>0.10803100775193808</v>
       </c>
       <c r="AZ8" s="4">
         <f t="shared" si="31"/>
-        <v>20.529999999999973</v>
+        <v>10.530000000000086</v>
       </c>
       <c r="BB8" s="8">
         <f t="shared" si="9"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="BH8" s="4">
         <f t="shared" si="25"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BI8" s="4">
         <f t="shared" si="32"/>
@@ -2327,10 +2327,10 @@
         <v>4.2499999999999717E-3</v>
       </c>
       <c r="Q9" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R9" s="4">
-        <v>632</v>
+        <v>316</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" si="36"/>
@@ -2399,27 +2399,27 @@
       </c>
       <c r="AM9" s="4">
         <f t="shared" si="3"/>
-        <v>1240</v>
+        <v>935</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="28"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO9" s="4">
         <f t="shared" si="4"/>
-        <v>1318.75</v>
+        <v>1002.75</v>
       </c>
       <c r="AP9" s="4">
         <f t="shared" si="5"/>
-        <v>78.75</v>
+        <v>67.75</v>
       </c>
       <c r="AQ9" s="13">
         <f t="shared" si="6"/>
-        <v>6.3508064516129031E-2</v>
+        <v>7.2459893048128346E-2</v>
       </c>
       <c r="AR9" s="4">
         <f t="shared" si="29"/>
-        <v>3.7000000000000455</v>
+        <v>2.6999999999999886</v>
       </c>
       <c r="AS9" s="10"/>
       <c r="AT9" s="8">
@@ -2428,27 +2428,27 @@
       </c>
       <c r="AU9" s="4">
         <f t="shared" si="18"/>
-        <v>1480</v>
+        <v>1175</v>
       </c>
       <c r="AV9" s="4">
         <f t="shared" si="30"/>
-        <v>630</v>
+        <v>530</v>
       </c>
       <c r="AW9" s="4">
         <f t="shared" si="19"/>
-        <v>1564.76</v>
+        <v>1248.76</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" si="7"/>
-        <v>84.759999999999991</v>
+        <v>73.759999999999991</v>
       </c>
       <c r="AY9" s="13">
         <f t="shared" si="8"/>
-        <v>5.7270270270270263E-2</v>
+        <v>6.277446808510638E-2</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="31"/>
-        <v>5.0800000000000409</v>
+        <v>4.0799999999999272</v>
       </c>
       <c r="BB9" s="8">
         <f t="shared" si="9"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="BH9" s="4">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI9" s="4">
         <f t="shared" si="32"/>
@@ -2545,10 +2545,10 @@
         <v>7.3738095238095297E-2</v>
       </c>
       <c r="Q10" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R10" s="4">
-        <v>634</v>
+        <v>317</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" si="36"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AM10" s="4">
         <f t="shared" si="3"/>
-        <v>1260</v>
+        <v>955</v>
       </c>
       <c r="AN10" s="4">
         <f t="shared" si="28"/>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="AO10" s="4">
         <f t="shared" si="4"/>
-        <v>1370.02</v>
+        <v>1053.02</v>
       </c>
       <c r="AP10" s="4">
         <f t="shared" si="5"/>
-        <v>110.01999999999998</v>
+        <v>98.019999999999982</v>
       </c>
       <c r="AQ10" s="13">
         <f t="shared" si="6"/>
-        <v>8.7317460317460308E-2</v>
+        <v>0.10263874345549737</v>
       </c>
       <c r="AR10" s="4">
         <f t="shared" si="29"/>
-        <v>31.269999999999982</v>
+        <v>30.269999999999982</v>
       </c>
       <c r="AS10" s="10"/>
       <c r="AT10" s="8">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AU10" s="4">
         <f t="shared" si="18"/>
-        <v>1530</v>
+        <v>1225</v>
       </c>
       <c r="AV10" s="4">
         <f t="shared" si="30"/>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="AW10" s="4">
         <f t="shared" si="19"/>
-        <v>1654.76</v>
+        <v>1337.76</v>
       </c>
       <c r="AX10" s="4">
         <f t="shared" si="7"/>
-        <v>124.75999999999999</v>
+        <v>112.75999999999999</v>
       </c>
       <c r="AY10" s="13">
         <f t="shared" si="8"/>
-        <v>8.1542483660130713E-2</v>
+        <v>9.2048979591836722E-2</v>
       </c>
       <c r="AZ10" s="4">
         <f t="shared" si="31"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB10" s="8">
         <f t="shared" si="9"/>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="BH10" s="4">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI10" s="4">
         <f t="shared" si="32"/>
@@ -2763,10 +2763,10 @@
         <v>8.6047619047619012E-2</v>
       </c>
       <c r="Q11" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R11" s="4">
-        <v>634</v>
+        <v>317</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" si="36"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AM11" s="4">
         <f t="shared" si="3"/>
-        <v>1360</v>
+        <v>1055</v>
       </c>
       <c r="AN11" s="4">
         <f t="shared" si="28"/>
@@ -2842,15 +2842,15 @@
       </c>
       <c r="AO11" s="4">
         <f t="shared" si="4"/>
-        <v>1500.19</v>
+        <v>1183.19</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" si="5"/>
-        <v>140.19000000000005</v>
+        <v>128.19000000000005</v>
       </c>
       <c r="AQ11" s="13">
         <f t="shared" si="6"/>
-        <v>0.10308088235294122</v>
+        <v>0.12150710900473939</v>
       </c>
       <c r="AR11" s="4">
         <f t="shared" si="29"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AU11" s="4">
         <f t="shared" si="18"/>
-        <v>1660</v>
+        <v>1355</v>
       </c>
       <c r="AV11" s="4">
         <f t="shared" si="30"/>
@@ -2871,15 +2871,15 @@
       </c>
       <c r="AW11" s="4">
         <f t="shared" si="19"/>
-        <v>1813.3000000000002</v>
+        <v>1496.3000000000002</v>
       </c>
       <c r="AX11" s="4">
         <f t="shared" si="7"/>
-        <v>153.30000000000018</v>
+        <v>141.30000000000018</v>
       </c>
       <c r="AY11" s="13">
         <f t="shared" si="8"/>
-        <v>9.2349397590361551E-2</v>
+        <v>0.10428044280442818</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" si="31"/>
@@ -2981,10 +2981,10 @@
         <v>9.6166666666666636E-2</v>
       </c>
       <c r="Q12" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R12" s="4">
-        <v>634</v>
+        <v>317</v>
       </c>
       <c r="S12" s="12">
         <f t="shared" si="36"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AM12" s="4">
         <f t="shared" si="3"/>
-        <v>1360</v>
+        <v>1055</v>
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="28"/>
@@ -3060,15 +3060,15 @@
       </c>
       <c r="AO12" s="4">
         <f t="shared" si="4"/>
-        <v>1510.6100000000001</v>
+        <v>1193.6100000000001</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="5"/>
-        <v>150.61000000000013</v>
+        <v>138.61000000000013</v>
       </c>
       <c r="AQ12" s="13">
         <f t="shared" si="6"/>
-        <v>0.11074264705882363</v>
+        <v>0.13138388625592429</v>
       </c>
       <c r="AR12" s="4">
         <f t="shared" si="29"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="18"/>
-        <v>1660</v>
+        <v>1355</v>
       </c>
       <c r="AV12" s="4">
         <f t="shared" si="30"/>
@@ -3089,15 +3089,15 @@
       </c>
       <c r="AW12" s="4">
         <f t="shared" si="19"/>
-        <v>1828.46</v>
+        <v>1511.46</v>
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="7"/>
-        <v>168.46000000000004</v>
+        <v>156.46000000000004</v>
       </c>
       <c r="AY12" s="13">
         <f t="shared" si="8"/>
-        <v>0.1014819277108434</v>
+        <v>0.1154686346863469</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="31"/>
@@ -3200,10 +3200,10 @@
         <v>0.10657142857142855</v>
       </c>
       <c r="Q13" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R13" s="4">
-        <v>634</v>
+        <v>317</v>
       </c>
       <c r="S13" s="12">
         <f t="shared" ref="S13" si="46">(R13-Q13)/Q13</f>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AM13" s="4">
         <f t="shared" si="3"/>
-        <v>1360</v>
+        <v>1055</v>
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="28"/>
@@ -3279,15 +3279,15 @@
       </c>
       <c r="AO13" s="4">
         <f t="shared" si="4"/>
-        <v>1514.98</v>
+        <v>1197.98</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="5"/>
-        <v>154.98000000000002</v>
+        <v>142.98000000000002</v>
       </c>
       <c r="AQ13" s="13">
         <f t="shared" si="6"/>
-        <v>0.11395588235294118</v>
+        <v>0.13552606635071091</v>
       </c>
       <c r="AR13" s="4">
         <f t="shared" si="29"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="18"/>
-        <v>1820</v>
+        <v>1515</v>
       </c>
       <c r="AV13" s="4">
         <f t="shared" si="30"/>
@@ -3308,15 +3308,15 @@
       </c>
       <c r="AW13" s="4">
         <f t="shared" si="19"/>
-        <v>2000.43</v>
+        <v>1683.43</v>
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="7"/>
-        <v>180.43000000000006</v>
+        <v>168.43000000000006</v>
       </c>
       <c r="AY13" s="13">
         <f t="shared" si="8"/>
-        <v>9.9137362637362669E-2</v>
+        <v>0.11117491749174922</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="31"/>
@@ -3418,10 +3418,10 @@
         <v>0.11692857142857147</v>
       </c>
       <c r="Q14" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R14" s="4">
-        <v>644.72</v>
+        <v>322.36</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ref="S14" si="52">(R14-Q14)/Q14</f>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AM14" s="4">
         <f t="shared" si="3"/>
-        <v>1360</v>
+        <v>1055</v>
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="28"/>
@@ -3497,19 +3497,19 @@
       </c>
       <c r="AO14" s="4">
         <f t="shared" si="4"/>
-        <v>1530.0500000000002</v>
+        <v>1207.69</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="5"/>
-        <v>170.05000000000018</v>
+        <v>152.69000000000005</v>
       </c>
       <c r="AQ14" s="13">
         <f t="shared" si="6"/>
-        <v>0.12503676470588249</v>
+        <v>0.14472985781990527</v>
       </c>
       <c r="AR14" s="4">
         <f t="shared" si="29"/>
-        <v>15.070000000000164</v>
+        <v>9.7100000000000364</v>
       </c>
       <c r="AS14" s="10"/>
       <c r="AT14" s="8">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="18"/>
-        <v>1950</v>
+        <v>1645</v>
       </c>
       <c r="AV14" s="4">
         <f t="shared" si="30"/>
@@ -3526,19 +3526,19 @@
       </c>
       <c r="AW14" s="4">
         <f t="shared" si="19"/>
-        <v>2152.5300000000002</v>
+        <v>1830.17</v>
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="7"/>
-        <v>202.5300000000002</v>
+        <v>185.17000000000007</v>
       </c>
       <c r="AY14" s="13">
         <f t="shared" si="8"/>
-        <v>0.10386153846153856</v>
+        <v>0.11256534954407299</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="31"/>
-        <v>22.100000000000136</v>
+        <v>16.740000000000009</v>
       </c>
       <c r="BB14" s="8">
         <f t="shared" si="9"/>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="25"/>
-        <v>10.720000000000027</v>
+        <v>5.3600000000000136</v>
       </c>
       <c r="BI14" s="4">
         <f t="shared" si="32"/>
@@ -3636,10 +3636,10 @@
         <v>9.2629032258064431E-2</v>
       </c>
       <c r="Q15" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R15" s="4">
-        <v>654.46</v>
+        <v>327.23</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" ref="S15" si="58">(R15-Q15)/Q15</f>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="AM15" s="4">
         <f t="shared" si="3"/>
-        <v>1560</v>
+        <v>1255</v>
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="28"/>
@@ -3715,19 +3715,19 @@
       </c>
       <c r="AO15" s="4">
         <f t="shared" si="4"/>
-        <v>1763.23</v>
+        <v>1436</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="5"/>
-        <v>203.23000000000002</v>
+        <v>181</v>
       </c>
       <c r="AQ15" s="13">
         <f t="shared" si="6"/>
-        <v>0.13027564102564104</v>
+        <v>0.14422310756972112</v>
       </c>
       <c r="AR15" s="4">
         <f t="shared" si="29"/>
-        <v>33.179999999999836</v>
+        <v>28.309999999999945</v>
       </c>
       <c r="AS15" s="10"/>
       <c r="AT15" s="8">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="18"/>
-        <v>2280</v>
+        <v>1975</v>
       </c>
       <c r="AV15" s="4">
         <f t="shared" si="30"/>
@@ -3744,19 +3744,19 @@
       </c>
       <c r="AW15" s="4">
         <f t="shared" si="19"/>
-        <v>2474.1400000000003</v>
+        <v>2146.91</v>
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="7"/>
-        <v>194.14000000000033</v>
+        <v>171.90999999999985</v>
       </c>
       <c r="AY15" s="13">
         <f t="shared" si="8"/>
-        <v>8.5149122807017683E-2</v>
+        <v>8.7043037974683476E-2</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="31"/>
-        <v>-8.3899999999998727</v>
+        <v>-13.260000000000218</v>
       </c>
       <c r="BB15" s="8">
         <f t="shared" ref="BB15" si="63">A15</f>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" ref="BH15" si="69">(R15-Q15)-(R14-Q14)</f>
-        <v>9.7400000000000091</v>
+        <v>4.8700000000000045</v>
       </c>
       <c r="BI15" s="4">
         <f t="shared" si="32"/>
@@ -3854,14 +3854,14 @@
         <v>9.6370967741935487E-2</v>
       </c>
       <c r="Q16" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R16" s="4">
-        <v>664.55</v>
+        <v>332.28</v>
       </c>
       <c r="S16" s="12">
         <f t="shared" ref="S16" si="75">(R16-Q16)/Q16</f>
-        <v>8.9426229508196647E-2</v>
+        <v>8.9442622950819589E-2</v>
       </c>
       <c r="T16" s="5">
         <v>40</v>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AM16" s="4">
         <f t="shared" si="3"/>
-        <v>1600</v>
+        <v>1295</v>
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="28"/>
@@ -3934,19 +3934,19 @@
       </c>
       <c r="AO16" s="4">
         <f t="shared" si="4"/>
-        <v>1818.0799999999997</v>
+        <v>1485.8099999999997</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="5"/>
-        <v>218.0799999999997</v>
+        <v>190.80999999999972</v>
       </c>
       <c r="AQ16" s="13">
         <f t="shared" si="6"/>
-        <v>0.13629999999999981</v>
+        <v>0.14734362934362913</v>
       </c>
       <c r="AR16" s="4">
         <f t="shared" si="29"/>
-        <v>14.849999999999682</v>
+        <v>9.8099999999997181</v>
       </c>
       <c r="AS16" s="10"/>
       <c r="AT16" s="8">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="18"/>
-        <v>2450</v>
+        <v>2145</v>
       </c>
       <c r="AV16" s="4">
         <f t="shared" si="30"/>
@@ -3963,19 +3963,19 @@
       </c>
       <c r="AW16" s="4">
         <f t="shared" si="19"/>
-        <v>2712.7</v>
+        <v>2380.4299999999994</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="7"/>
-        <v>262.69999999999982</v>
+        <v>235.42999999999938</v>
       </c>
       <c r="AY16" s="13">
         <f t="shared" si="8"/>
-        <v>0.1072244897959183</v>
+        <v>0.10975757575757547</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="31"/>
-        <v>68.559999999999491</v>
+        <v>63.519999999999527</v>
       </c>
       <c r="BB16" s="8">
         <f t="shared" ref="BB16" si="81">A16</f>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" ref="BH16" si="87">(R16-Q16)-(R15-Q15)</f>
-        <v>10.089999999999918</v>
+        <v>5.0499999999999545</v>
       </c>
       <c r="BI16" s="4">
         <f t="shared" si="32"/>
@@ -4073,14 +4073,14 @@
         <v>0.10343548387096774</v>
       </c>
       <c r="Q17" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R17" s="4">
-        <v>666.19</v>
+        <v>333.1</v>
       </c>
       <c r="S17" s="12">
         <f t="shared" ref="S17" si="94">(R17-Q17)/Q17</f>
-        <v>9.2114754098360743E-2</v>
+        <v>9.2131147540983685E-2</v>
       </c>
       <c r="T17" s="5">
         <v>70</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AM17" s="4">
         <f t="shared" si="3"/>
-        <v>1844.99</v>
+        <v>1539.99</v>
       </c>
       <c r="AN17" s="4">
         <f t="shared" ref="AN17" si="103">AM17-AM16</f>
@@ -4153,19 +4153,19 @@
       </c>
       <c r="AO17" s="4">
         <f t="shared" si="4"/>
-        <v>2070.6999999999998</v>
+        <v>1737.6100000000001</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" ref="AP17" si="104">AO17-AM17</f>
-        <v>225.70999999999981</v>
+        <v>197.62000000000012</v>
       </c>
       <c r="AQ17" s="13">
         <f t="shared" ref="AQ17" si="105">AP17/AM17</f>
-        <v>0.12233670643201308</v>
+        <v>0.12832550860719882</v>
       </c>
       <c r="AR17" s="4">
         <f t="shared" ref="AR17" si="106">AP17-AP16</f>
-        <v>7.6300000000001091</v>
+        <v>6.8100000000004002</v>
       </c>
       <c r="AS17" s="10"/>
       <c r="AT17" s="8">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AU17" s="4">
         <f t="shared" ref="AU17" si="108">AE17+AM17</f>
-        <v>2824.99</v>
+        <v>2519.9899999999998</v>
       </c>
       <c r="AV17" s="4">
         <f t="shared" ref="AV17" si="109">AU17-AU16</f>
@@ -4182,19 +4182,19 @@
       </c>
       <c r="AW17" s="4">
         <f t="shared" ref="AW17" si="110">AG17+AO17</f>
-        <v>3142.2</v>
+        <v>2809.11</v>
       </c>
       <c r="AX17" s="4">
         <f t="shared" ref="AX17" si="111">AW17-AU17</f>
-        <v>317.21000000000004</v>
+        <v>289.12000000000035</v>
       </c>
       <c r="AY17" s="13">
         <f t="shared" ref="AY17" si="112">AX17/AU17</f>
-        <v>0.11228712314025893</v>
+        <v>0.11473061401037321</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" ref="AZ17" si="113">AX17-AX16</f>
-        <v>54.510000000000218</v>
+        <v>53.690000000000964</v>
       </c>
       <c r="BB17" s="8">
         <f t="shared" ref="BB17" si="114">A17</f>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" ref="BH17" si="120">(R17-Q17)-(R16-Q16)</f>
-        <v>1.6400000000001</v>
+        <v>0.82000000000005002</v>
       </c>
       <c r="BI17" s="4">
         <f t="shared" si="32"/>
@@ -4292,10 +4292,10 @@
         <v>0.11838709677419351</v>
       </c>
       <c r="Q18" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R18" s="4">
-        <v>667.84</v>
+        <v>333.92</v>
       </c>
       <c r="S18" s="12">
         <f t="shared" ref="S18" si="127">(R18-Q18)/Q18</f>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AM18" s="4">
         <f t="shared" si="3"/>
-        <v>1953.95</v>
+        <v>1648.95</v>
       </c>
       <c r="AN18" s="4">
         <f t="shared" ref="AN18" si="136">AM18-AM17</f>
@@ -4372,19 +4372,19 @@
       </c>
       <c r="AO18" s="4">
         <f t="shared" si="4"/>
-        <v>2191.48</v>
+        <v>1857.5600000000002</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" ref="AP18" si="137">AO18-AM18</f>
-        <v>237.52999999999997</v>
+        <v>208.61000000000013</v>
       </c>
       <c r="AQ18" s="13">
         <f t="shared" ref="AQ18" si="138">AP18/AM18</f>
-        <v>0.12156401136160085</v>
+        <v>0.12651080990933633</v>
       </c>
       <c r="AR18" s="4">
         <f t="shared" ref="AR18" si="139">AP18-AP17</f>
-        <v>11.820000000000164</v>
+        <v>10.990000000000009</v>
       </c>
       <c r="AS18" s="10"/>
       <c r="AT18" s="8">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AU18" s="4">
         <f t="shared" ref="AU18" si="141">AE18+AM18</f>
-        <v>3063.95</v>
+        <v>2758.95</v>
       </c>
       <c r="AV18" s="4">
         <f t="shared" ref="AV18" si="142">AU18-AU17</f>
@@ -4401,19 +4401,19 @@
       </c>
       <c r="AW18" s="4">
         <f t="shared" ref="AW18" si="143">AG18+AO18</f>
-        <v>3408.0299999999997</v>
+        <v>3074.11</v>
       </c>
       <c r="AX18" s="4">
         <f t="shared" ref="AX18" si="144">AW18-AU18</f>
-        <v>344.07999999999993</v>
+        <v>315.16000000000031</v>
       </c>
       <c r="AY18" s="13">
         <f t="shared" ref="AY18" si="145">AX18/AU18</f>
-        <v>0.11229948269390817</v>
+        <v>0.1142318635712863</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" ref="AZ18" si="146">AX18-AX17</f>
-        <v>26.869999999999891</v>
+        <v>26.039999999999964</v>
       </c>
       <c r="BB18" s="8">
         <f t="shared" ref="BB18" si="147">A18</f>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" ref="BH18" si="153">(R18-Q18)-(R17-Q17)</f>
-        <v>1.6499999999999773</v>
+        <v>0.81999999999999318</v>
       </c>
       <c r="BI18" s="4">
         <f t="shared" si="32"/>
@@ -4511,10 +4511,10 @@
         <v>0.12248387096774202</v>
       </c>
       <c r="Q19" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R19" s="4">
-        <v>669.6</v>
+        <v>334.8</v>
       </c>
       <c r="S19" s="12">
         <f t="shared" ref="S19" si="160">(R19-Q19)/Q19</f>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM19" s="4">
         <f>H19+K19+N19+Q19+T19+W19+Z19</f>
-        <v>1953.95</v>
+        <v>1648.95</v>
       </c>
       <c r="AN19" s="4">
         <f t="shared" ref="AN19" si="169">AM19-AM18</f>
@@ -4591,19 +4591,19 @@
       </c>
       <c r="AO19" s="4">
         <f>I19+L19+O19+R19+U19+X19+AA19</f>
-        <v>2198.7199999999998</v>
+        <v>1863.9199999999998</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" ref="AP19" si="170">AO19-AM19</f>
-        <v>244.76999999999975</v>
+        <v>214.9699999999998</v>
       </c>
       <c r="AQ19" s="13">
         <f t="shared" ref="AQ19" si="171">AP19/AM19</f>
-        <v>0.12526932623659753</v>
+        <v>0.13036780981836915</v>
       </c>
       <c r="AR19" s="4">
         <f t="shared" ref="AR19" si="172">AP19-AP18</f>
-        <v>7.2399999999997817</v>
+        <v>6.3599999999996726</v>
       </c>
       <c r="AS19" s="10"/>
       <c r="AT19" s="8">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AU19" s="4">
         <f t="shared" ref="AU19" si="174">AE19+AM19</f>
-        <v>3193.95</v>
+        <v>2888.95</v>
       </c>
       <c r="AV19" s="4">
         <f t="shared" ref="AV19" si="175">AU19-AU18</f>
@@ -4620,19 +4620,19 @@
       </c>
       <c r="AW19" s="4">
         <f t="shared" ref="AW19" si="176">AG19+AO19</f>
-        <v>3536.5899999999997</v>
+        <v>3201.79</v>
       </c>
       <c r="AX19" s="4">
         <f t="shared" ref="AX19" si="177">AW19-AU19</f>
-        <v>342.63999999999987</v>
+        <v>312.84000000000015</v>
       </c>
       <c r="AY19" s="13">
         <f t="shared" ref="AY19" si="178">AX19/AU19</f>
-        <v>0.10727782213246917</v>
+        <v>0.10828847851295459</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" ref="AZ19" si="179">AX19-AX18</f>
-        <v>-1.4400000000000546</v>
+        <v>-2.3200000000001637</v>
       </c>
       <c r="BB19" s="8">
         <f t="shared" ref="BB19" si="180">A19</f>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" ref="BH19" si="186">(R19-Q19)-(R18-Q18)</f>
-        <v>1.7599999999999909</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="BI19" s="4">
         <f t="shared" si="32"/>
@@ -4730,14 +4730,14 @@
         <v>0.12740322580645164</v>
       </c>
       <c r="Q20" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R20" s="4">
-        <v>678.45</v>
+        <v>339.23</v>
       </c>
       <c r="S20" s="12">
         <f t="shared" ref="S20" si="193">(R20-Q20)/Q20</f>
-        <v>0.11221311475409844</v>
+        <v>0.11222950819672137</v>
       </c>
       <c r="T20" s="5">
         <v>80</v>
@@ -4803,27 +4803,27 @@
       </c>
       <c r="AM20" s="4">
         <f>H20+K20+N20+Q20+T20+W20+Z20</f>
-        <v>2263.9499999999998</v>
+        <v>1958.95</v>
       </c>
       <c r="AN20" s="4">
         <f t="shared" ref="AN20" si="202">AM20-AM19</f>
-        <v>309.99999999999977</v>
+        <v>310</v>
       </c>
       <c r="AO20" s="4">
         <f>I20+L20+O20+R20+U20+X20+AA20</f>
-        <v>2523.6000000000004</v>
+        <v>2184.38</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" ref="AP20" si="203">AO20-AM20</f>
-        <v>259.65000000000055</v>
+        <v>225.43000000000006</v>
       </c>
       <c r="AQ20" s="13">
         <f t="shared" ref="AQ20" si="204">AP20/AM20</f>
-        <v>0.11468892864241727</v>
+        <v>0.11507695449092629</v>
       </c>
       <c r="AR20" s="4">
         <f t="shared" ref="AR20" si="205">AP20-AP19</f>
-        <v>14.880000000000791</v>
+        <v>10.460000000000264</v>
       </c>
       <c r="AS20" s="10"/>
       <c r="AT20" s="8">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AU20" s="4">
         <f t="shared" ref="AU20" si="207">AE20+AM20</f>
-        <v>3633.95</v>
+        <v>3328.95</v>
       </c>
       <c r="AV20" s="4">
         <f t="shared" ref="AV20" si="208">AU20-AU19</f>
@@ -4840,19 +4840,19 @@
       </c>
       <c r="AW20" s="4">
         <f t="shared" ref="AW20" si="209">AG20+AO20</f>
-        <v>4021.3</v>
+        <v>3682.08</v>
       </c>
       <c r="AX20" s="4">
         <f t="shared" ref="AX20" si="210">AW20-AU20</f>
-        <v>387.35000000000036</v>
+        <v>353.13000000000011</v>
       </c>
       <c r="AY20" s="13">
         <f t="shared" ref="AY20" si="211">AX20/AU20</f>
-        <v>0.10659200044029235</v>
+        <v>0.10607849321858248</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" ref="AZ20" si="212">AX20-AX19</f>
-        <v>44.710000000000491</v>
+        <v>40.289999999999964</v>
       </c>
       <c r="BB20" s="8">
         <f t="shared" ref="BB20" si="213">A20</f>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" ref="BH20" si="219">(R20-Q20)-(R19-Q19)</f>
-        <v>8.8500000000000227</v>
+        <v>4.4300000000000068</v>
       </c>
       <c r="BI20" s="4">
         <f t="shared" ref="BI20" si="220">(U20-T20)-(U19-T19)</f>
@@ -4953,14 +4953,14 @@
         <v>0.13695161290322574</v>
       </c>
       <c r="Q21" s="5">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R21" s="4">
-        <v>687.59</v>
+        <v>343.8</v>
       </c>
       <c r="S21" s="12">
         <f t="shared" ref="S21" si="228">(R21-Q21)/Q21</f>
-        <v>0.12719672131147547</v>
+        <v>0.12721311475409841</v>
       </c>
       <c r="T21" s="5">
         <v>80</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AM21" s="4">
         <f>H21+K21+N21+Q21+T21+W21+Z21</f>
-        <v>2263.9499999999998</v>
+        <v>1958.95</v>
       </c>
       <c r="AN21" s="4">
         <f t="shared" ref="AN21" si="237">AM21-AM20</f>
@@ -5035,19 +5035,19 @@
       </c>
       <c r="AO21" s="4">
         <f>I21+L21+O21+R21+U21+X21+AA21</f>
-        <v>2549.5100000000007</v>
+        <v>2205.7200000000003</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" ref="AP21" si="238">AO21-AM21</f>
-        <v>285.56000000000085</v>
+        <v>246.77000000000021</v>
       </c>
       <c r="AQ21" s="13">
         <f t="shared" ref="AQ21" si="239">AP21/AM21</f>
-        <v>0.12613352768391567</v>
+        <v>0.12597054544526415</v>
       </c>
       <c r="AR21" s="4">
         <f t="shared" ref="AR21" si="240">AP21-AP20</f>
-        <v>25.910000000000309</v>
+        <v>21.340000000000146</v>
       </c>
       <c r="AS21" s="10"/>
       <c r="AT21" s="8">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AU21" s="4">
         <f t="shared" ref="AU21" si="242">AE21+AM21</f>
-        <v>3763.95</v>
+        <v>3458.95</v>
       </c>
       <c r="AV21" s="4">
         <f t="shared" ref="AV21" si="243">AU21-AU20</f>
@@ -5064,19 +5064,19 @@
       </c>
       <c r="AW21" s="4">
         <f t="shared" ref="AW21" si="244">AG21+AO21</f>
-        <v>4184.130000000001</v>
+        <v>3840.34</v>
       </c>
       <c r="AX21" s="4">
         <f t="shared" ref="AX21" si="245">AW21-AU21</f>
-        <v>420.1800000000012</v>
+        <v>381.39000000000033</v>
       </c>
       <c r="AY21" s="13">
         <f t="shared" ref="AY21" si="246">AX21/AU21</f>
-        <v>0.11163272625831938</v>
+        <v>0.11026178464562955</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" ref="AZ21" si="247">AX21-AX20</f>
-        <v>32.830000000000837</v>
+        <v>28.260000000000218</v>
       </c>
       <c r="BB21" s="8">
         <f t="shared" ref="BB21" si="248">A21</f>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" ref="BH21" si="254">(R21-Q21)-(R20-Q20)</f>
-        <v>9.1399999999999864</v>
+        <v>4.5699999999999932</v>
       </c>
       <c r="BI21" s="4">
         <f t="shared" ref="BI21" si="255">(U21-T21)-(U20-T20)</f>
